--- a/IT授業内容(智源).xlsx
+++ b/IT授業内容(智源).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\study\saisk\java\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tech\git20220205\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0E249-D310-4136-94F8-E91E82F9010E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4012B2CD-9390-4C0C-B8AC-C38F08640958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必要ツール" sheetId="3" r:id="rId1"/>
@@ -464,7 +464,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="532">
   <si>
     <t>日付</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2466,10 +2466,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>http://woodybells.com/winshot.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://winmergejp.bitbucket.io/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2583,6 +2579,17 @@
     <t>仕事流れ
 EXCELコツなど</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-zip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.7-zip.org/download.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://woodybells.com/softs/ws153a.zip</t>
   </si>
 </sst>
 </file>
@@ -4754,10 +4761,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D5" s="45" t="s">
         <v>514</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -4793,7 +4800,7 @@
         <v>509</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -4805,7 +4812,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -4817,7 +4824,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -4825,8 +4832,12 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="50"/>
+      <c r="C11" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="44">
@@ -4869,12 +4880,13 @@
     <hyperlink ref="D4" r:id="rId2" xr:uid="{22AEB766-92F6-470E-8207-79A0C64B1CF8}"/>
     <hyperlink ref="D6" r:id="rId3" xr:uid="{2009036F-2C07-49EF-85D8-F94C1CBB5BD2}"/>
     <hyperlink ref="D7" r:id="rId4" xr:uid="{1A5FFFE6-4967-4225-9B2C-3F0BCFF3D5FE}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{D3D2EB3E-CEFB-4BE3-BF1C-B9A78EA08C47}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{32B20C4C-7BFD-48DC-BB0A-BC6915508E6F}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{204584A2-B173-4E3E-8317-F0E215C42A19}"/>
-    <hyperlink ref="D5" r:id="rId8" xr:uid="{4FA2EA2B-CC81-41A0-9980-C94CAE5CEF6B}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{32B20C4C-7BFD-48DC-BB0A-BC6915508E6F}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{204584A2-B173-4E3E-8317-F0E215C42A19}"/>
+    <hyperlink ref="D5" r:id="rId7" xr:uid="{4FA2EA2B-CC81-41A0-9980-C94CAE5CEF6B}"/>
+    <hyperlink ref="D11" r:id="rId8" xr:uid="{2C15FE46-DE0D-4EB9-8911-16F8C2AD9C51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -6312,7 +6324,7 @@
         <v>31</v>
       </c>
       <c r="H12" s="56" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="2:10">
@@ -6373,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H15" s="59" t="s">
         <v>42</v>
@@ -6398,7 +6410,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H16" s="57"/>
     </row>
@@ -6694,7 +6706,7 @@
         <v>22</v>
       </c>
       <c r="H30" s="57" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" spans="2:10">
@@ -6756,7 +6768,7 @@
         <v>24</v>
       </c>
       <c r="H33" s="56" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="2:8">
@@ -6818,7 +6830,7 @@
         <v>484</v>
       </c>
       <c r="H36" s="56" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -6950,7 +6962,7 @@
         <v>33</v>
       </c>
       <c r="H3" s="56" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J3" s="33">
         <v>44689</v>
@@ -7442,7 +7454,7 @@
         <v>37</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J27" s="33">
         <v>44745</v>
@@ -7504,10 +7516,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H30" s="57" t="s">
         <v>520</v>
-      </c>
-      <c r="H30" s="57" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="31" spans="2:10">
@@ -7526,7 +7538,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H31" s="57"/>
     </row>
@@ -7546,13 +7558,13 @@
         <v>3</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H32" s="57"/>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="63" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C33" s="6">
         <f>$J$27+14</f>
@@ -7614,7 +7626,7 @@
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="63" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C36" s="6">
         <f>$J$27+21</f>
@@ -7630,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H36" s="57"/>
     </row>
@@ -7650,7 +7662,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H37" s="57"/>
     </row>
@@ -7670,7 +7682,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H38" s="58"/>
     </row>
@@ -7681,6 +7693,7 @@
     <mergeCell ref="H30:H32"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="H36:H38"/>
+    <mergeCell ref="B33:B35"/>
     <mergeCell ref="B3:B26"/>
     <mergeCell ref="B27:B32"/>
     <mergeCell ref="H3:H5"/>
@@ -7691,7 +7704,6 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="H24:H26"/>
-    <mergeCell ref="B33:B35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9392,7 +9404,7 @@
     </row>
     <row r="243" spans="2:2" ht="16">
       <c r="B243" s="13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="244" spans="2:2">
@@ -10210,9 +10222,9 @@
     <row r="94" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="95" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="96" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="97" s="22" customFormat="1"/>
-    <row r="98" s="22" customFormat="1"/>
-    <row r="99" s="22" customFormat="1"/>
+    <row r="97" s="22" customFormat="1" ht="21"/>
+    <row r="98" s="22" customFormat="1" ht="21"/>
+    <row r="99" s="22" customFormat="1" ht="21"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/IT授業内容(智源).xlsx
+++ b/IT授業内容(智源).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tech\git20220205\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4012B2CD-9390-4C0C-B8AC-C38F08640958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF2DC00-519E-49C8-838D-035D338476C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4150" yWindow="2460" windowWidth="16160" windowHeight="5660" tabRatio="809" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必要ツール" sheetId="3" r:id="rId1"/>
@@ -23,12 +23,13 @@
     <sheet name="JAVA宿題" sheetId="4" r:id="rId8"/>
     <sheet name="SQL宿題1" sheetId="6" r:id="rId9"/>
     <sheet name="SQL宿題2" sheetId="16" r:id="rId10"/>
-    <sheet name="１" sheetId="9" state="hidden" r:id="rId11"/>
-    <sheet name="2" sheetId="10" state="hidden" r:id="rId12"/>
-    <sheet name="３" sheetId="11" state="hidden" r:id="rId13"/>
-    <sheet name="４" sheetId="12" state="hidden" r:id="rId14"/>
-    <sheet name="５" sheetId="13" state="hidden" r:id="rId15"/>
-    <sheet name="6" sheetId="14" state="hidden" r:id="rId16"/>
+    <sheet name="JVM里变量加载图" sheetId="18" r:id="rId11"/>
+    <sheet name="１" sheetId="9" state="hidden" r:id="rId12"/>
+    <sheet name="2" sheetId="10" state="hidden" r:id="rId13"/>
+    <sheet name="３" sheetId="11" state="hidden" r:id="rId14"/>
+    <sheet name="４" sheetId="12" state="hidden" r:id="rId15"/>
+    <sheet name="５" sheetId="13" state="hidden" r:id="rId16"/>
+    <sheet name="6" sheetId="14" state="hidden" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'ITフレームワーク(４～６ケ月)'!$A$1:$H$38</definedName>
@@ -464,7 +465,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="560">
   <si>
     <t>日付</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2590,6 +2591,118 @@
   </si>
   <si>
     <t>http://woodybells.com/softs/ws153a.zip</t>
+  </si>
+  <si>
+    <t>栈区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8种简单数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boolean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>new Object()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>final</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAVA文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字节码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JVM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局内存（字节码里已经存在）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>windows</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加载内存顺序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TreeMap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2741,7 +2854,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2784,8 +2897,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -3071,13 +3196,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -3201,6 +3406,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3221,6 +3481,455 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>237737</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>58814</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D0773B6-4D86-4043-BC9C-FF90AF47B82F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="355600"/>
+          <a:ext cx="8822937" cy="5392814"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>656356</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>138622</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F7C6FCC-2FE1-489D-81A6-EF13E20CD55D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8375650" y="5003800"/>
+          <a:ext cx="865906" cy="468822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>492358</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>19218</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>94245</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="矢印: 右 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF75AA88-D639-4EFF-BE1C-B94BEFA32AC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="3912842" flipH="1">
+          <a:off x="8881182" y="5549594"/>
+          <a:ext cx="655039" cy="262287"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>531335</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>88901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2A2AD1-66BC-4387-ACFA-FFD31111596A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="9067801"/>
+          <a:ext cx="7795735" cy="5600700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F80B9340-6C08-4EC2-AF88-A122E0718AF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1231900" y="11207750"/>
+          <a:ext cx="2470150" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>181206</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>57316</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>443493</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="矢印: 右 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8324A7D2-8CF8-4C0F-B37A-C1B149377A8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="3912842" flipH="1">
+          <a:off x="3286830" y="11632892"/>
+          <a:ext cx="655039" cy="262287"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>97505</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>170357</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999D001E-C8EE-4B51-91CA-54915DEF5994}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="400050"/>
+          <a:ext cx="7361905" cy="8742857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>389314</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>81005</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C225BB85-7FCD-4978-A9D6-B319B49DD324}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="139700" y="317500"/>
+          <a:ext cx="9685714" cy="12361905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3391,7 +4100,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3882,7 +4591,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4151,7 +4860,65 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{947D583A-162C-4369-8074-8660A6B82591}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2921000" y="1924050"/>
+          <a:ext cx="19050" cy="2165350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4199,7 +4966,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4248,7 +5015,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4297,7 +5064,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4335,104 +5102,6 @@
         <a:xfrm>
           <a:off x="254000" y="203200"/>
           <a:ext cx="8019048" cy="7761905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>97505</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>170357</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999D001E-C8EE-4B51-91CA-54915DEF5994}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="660400" y="400050"/>
-          <a:ext cx="7361905" cy="8742857"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>389314</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>81005</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C225BB85-7FCD-4978-A9D6-B319B49DD324}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="139700" y="317500"/>
-          <a:ext cx="9685714" cy="12361905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5416,6 +6085,660 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A7714B-D9DD-416F-B392-2E2CEF359F1C}">
+  <sheetPr>
+    <tabColor theme="7"/>
+  </sheetPr>
+  <dimension ref="C2:Z27"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="20" width="8.6640625" style="67"/>
+    <col min="21" max="26" width="8.6640625" style="89"/>
+    <col min="27" max="16384" width="8.6640625" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:26">
+      <c r="F2" s="67" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="3" spans="3:26">
+      <c r="U3" s="90"/>
+      <c r="V3" s="90"/>
+      <c r="W3" s="90"/>
+      <c r="X3" s="90"/>
+      <c r="Y3" s="90"/>
+    </row>
+    <row r="4" spans="3:26">
+      <c r="U4" s="90">
+        <v>1</v>
+      </c>
+      <c r="V4" s="90"/>
+      <c r="W4" s="90">
+        <v>2</v>
+      </c>
+      <c r="X4" s="90"/>
+      <c r="Y4" s="90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="3:26">
+      <c r="U5" s="90" t="s">
+        <v>550</v>
+      </c>
+      <c r="V5" s="90" t="s">
+        <v>551</v>
+      </c>
+      <c r="W5" s="90" t="s">
+        <v>552</v>
+      </c>
+      <c r="X5" s="90" t="s">
+        <v>551</v>
+      </c>
+      <c r="Y5" s="90" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="6" spans="3:26" ht="14.5" thickBot="1"/>
+    <row r="7" spans="3:26">
+      <c r="C7" s="68"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="91"/>
+      <c r="V7" s="91"/>
+      <c r="W7" s="91"/>
+      <c r="X7" s="91"/>
+      <c r="Y7" s="91"/>
+      <c r="Z7" s="92"/>
+    </row>
+    <row r="8" spans="3:26" ht="14.5" thickBot="1">
+      <c r="C8" s="71"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72" t="s">
+        <v>554</v>
+      </c>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72" t="s">
+        <v>556</v>
+      </c>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="93"/>
+      <c r="V8" s="93"/>
+      <c r="W8" s="93" t="s">
+        <v>557</v>
+      </c>
+      <c r="X8" s="93"/>
+      <c r="Y8" s="93"/>
+      <c r="Z8" s="94"/>
+    </row>
+    <row r="9" spans="3:26">
+      <c r="C9" s="71"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="77" t="s">
+        <v>555</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="69"/>
+      <c r="T9" s="69"/>
+      <c r="U9" s="92"/>
+      <c r="V9" s="93"/>
+      <c r="W9" s="97"/>
+      <c r="X9" s="91"/>
+      <c r="Y9" s="92"/>
+      <c r="Z9" s="94"/>
+    </row>
+    <row r="10" spans="3:26" ht="14.5" thickBot="1">
+      <c r="C10" s="71"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="93"/>
+      <c r="W10" s="98"/>
+      <c r="X10" s="93"/>
+      <c r="Y10" s="94"/>
+      <c r="Z10" s="94"/>
+    </row>
+    <row r="11" spans="3:26">
+      <c r="C11" s="71"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="83" t="s">
+        <v>543</v>
+      </c>
+      <c r="H11" s="83" t="s">
+        <v>544</v>
+      </c>
+      <c r="I11" s="83" t="s">
+        <v>547</v>
+      </c>
+      <c r="J11" s="83" t="s">
+        <v>545</v>
+      </c>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="93"/>
+      <c r="W11" s="98"/>
+      <c r="X11" s="93"/>
+      <c r="Y11" s="94"/>
+      <c r="Z11" s="94"/>
+    </row>
+    <row r="12" spans="3:26">
+      <c r="C12" s="71"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="93"/>
+      <c r="Y12" s="94"/>
+      <c r="Z12" s="94"/>
+    </row>
+    <row r="13" spans="3:26">
+      <c r="C13" s="71"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="J13" s="84" t="s">
+        <v>546</v>
+      </c>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="72"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="93"/>
+      <c r="W13" s="98"/>
+      <c r="X13" s="93"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+    </row>
+    <row r="14" spans="3:26">
+      <c r="C14" s="71"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84" t="s">
+        <v>549</v>
+      </c>
+      <c r="J14" s="84"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="93"/>
+      <c r="W14" s="98"/>
+      <c r="X14" s="93"/>
+      <c r="Y14" s="94"/>
+      <c r="Z14" s="94"/>
+    </row>
+    <row r="15" spans="3:26">
+      <c r="C15" s="71"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="93"/>
+      <c r="W15" s="98"/>
+      <c r="X15" s="93"/>
+      <c r="Y15" s="94"/>
+      <c r="Z15" s="94"/>
+    </row>
+    <row r="16" spans="3:26" ht="14.5" thickBot="1">
+      <c r="C16" s="71"/>
+      <c r="D16" s="72" t="s">
+        <v>558</v>
+      </c>
+      <c r="E16" s="73"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="85"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="87"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="93"/>
+      <c r="W16" s="98"/>
+      <c r="X16" s="93"/>
+      <c r="Y16" s="94"/>
+      <c r="Z16" s="94"/>
+    </row>
+    <row r="17" spans="3:26" ht="14.5" thickBot="1">
+      <c r="C17" s="71"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="86"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="94"/>
+      <c r="V17" s="93"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="93"/>
+      <c r="Y17" s="94"/>
+      <c r="Z17" s="94"/>
+    </row>
+    <row r="18" spans="3:26">
+      <c r="C18" s="71"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="71" t="s">
+        <v>532</v>
+      </c>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="68" t="s">
+        <v>533</v>
+      </c>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="93"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="93"/>
+      <c r="Y18" s="94"/>
+      <c r="Z18" s="94"/>
+    </row>
+    <row r="19" spans="3:26">
+      <c r="C19" s="71"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="71" t="s">
+        <v>534</v>
+      </c>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="72" t="s">
+        <v>542</v>
+      </c>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="93"/>
+      <c r="W19" s="98"/>
+      <c r="X19" s="93"/>
+      <c r="Y19" s="94"/>
+      <c r="Z19" s="94"/>
+    </row>
+    <row r="20" spans="3:26">
+      <c r="C20" s="71"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="71" t="s">
+        <v>535</v>
+      </c>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="94"/>
+      <c r="V20" s="93"/>
+      <c r="W20" s="98"/>
+      <c r="X20" s="93"/>
+      <c r="Y20" s="94"/>
+      <c r="Z20" s="94"/>
+    </row>
+    <row r="21" spans="3:26">
+      <c r="C21" s="71"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="71" t="s">
+        <v>536</v>
+      </c>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="93"/>
+      <c r="W21" s="98"/>
+      <c r="X21" s="93"/>
+      <c r="Y21" s="94"/>
+      <c r="Z21" s="94"/>
+    </row>
+    <row r="22" spans="3:26">
+      <c r="C22" s="71"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="71" t="s">
+        <v>537</v>
+      </c>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="71"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="93"/>
+      <c r="W22" s="98"/>
+      <c r="X22" s="93"/>
+      <c r="Y22" s="94"/>
+      <c r="Z22" s="94"/>
+    </row>
+    <row r="23" spans="3:26">
+      <c r="C23" s="71"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="71" t="s">
+        <v>538</v>
+      </c>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="94"/>
+      <c r="V23" s="93"/>
+      <c r="W23" s="98"/>
+      <c r="X23" s="93"/>
+      <c r="Y23" s="94"/>
+      <c r="Z23" s="94"/>
+    </row>
+    <row r="24" spans="3:26">
+      <c r="C24" s="71"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="71" t="s">
+        <v>539</v>
+      </c>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="94"/>
+      <c r="V24" s="93"/>
+      <c r="W24" s="98"/>
+      <c r="X24" s="93"/>
+      <c r="Y24" s="94"/>
+      <c r="Z24" s="94"/>
+    </row>
+    <row r="25" spans="3:26">
+      <c r="C25" s="71"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="71" t="s">
+        <v>540</v>
+      </c>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="94"/>
+      <c r="V25" s="93"/>
+      <c r="W25" s="98"/>
+      <c r="X25" s="93"/>
+      <c r="Y25" s="94"/>
+      <c r="Z25" s="94"/>
+    </row>
+    <row r="26" spans="3:26" ht="14.5" thickBot="1">
+      <c r="C26" s="71"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74" t="s">
+        <v>541</v>
+      </c>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="76"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="96"/>
+      <c r="V26" s="93"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="94"/>
+    </row>
+    <row r="27" spans="3:26" ht="14.5" thickBot="1">
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="75"/>
+      <c r="S27" s="75"/>
+      <c r="T27" s="75"/>
+      <c r="U27" s="95"/>
+      <c r="V27" s="95"/>
+      <c r="W27" s="95"/>
+      <c r="X27" s="95"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="96"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF30867F-4987-428B-B1BA-79BEE1AC7E24}">
   <dimension ref="B1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5486,7 +6809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D3055-B4C0-44F8-BC38-3332800489E4}">
   <dimension ref="B1:S32"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5661,7 +6984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBA7452-ADCF-4916-B20B-0512AE3ED3F2}">
   <dimension ref="B1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5730,7 +7053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A228C4-8BB0-42F2-86E2-63F3E8493370}">
   <dimension ref="B1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5791,7 +7114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C125254-9191-4F9A-8C38-B14BF103FA27}">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5846,7 +7169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E4EC444-DA0C-43AC-8DA7-D83AAF18CFD5}">
   <dimension ref="B1:S26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7688,12 +9011,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="H33:H35"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="B33:B35"/>
     <mergeCell ref="B3:B26"/>
     <mergeCell ref="B27:B32"/>
     <mergeCell ref="H3:H5"/>
@@ -7704,6 +9021,12 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="H24:H26"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="H33:H35"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="B33:B35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7719,202 +9042,203 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B2:B40"/>
+  <dimension ref="B70:B108"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="2" spans="2:2" ht="15.5">
-      <c r="B2" s="11" t="s">
+    <row r="70" spans="2:2" ht="15.5">
+      <c r="B70" s="11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="15.5">
-      <c r="B4" s="11" t="s">
+    <row r="72" spans="2:2" ht="15.5">
+      <c r="B72" s="11" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="15.5">
-      <c r="B5" s="11" t="s">
+    <row r="73" spans="2:2" ht="15.5">
+      <c r="B73" s="11" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="15.5">
-      <c r="B6" s="11" t="s">
+    <row r="74" spans="2:2" ht="15.5">
+      <c r="B74" s="11" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="15.5">
-      <c r="B7" s="11" t="s">
+    <row r="75" spans="2:2" ht="15.5">
+      <c r="B75" s="11" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="15.5">
-      <c r="B8" s="11" t="s">
+    <row r="76" spans="2:2" ht="15.5">
+      <c r="B76" s="11" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="15.5">
-      <c r="B9" s="11" t="s">
+    <row r="77" spans="2:2" ht="15.5">
+      <c r="B77" s="11" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="15.5">
-      <c r="B10" s="11" t="s">
+    <row r="78" spans="2:2" ht="15.5">
+      <c r="B78" s="11" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="15.5">
-      <c r="B11" s="11" t="s">
+    <row r="79" spans="2:2" ht="15.5">
+      <c r="B79" s="11" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="15.5">
-      <c r="B12" s="11" t="s">
+    <row r="80" spans="2:2" ht="15.5">
+      <c r="B80" s="11" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="15.5">
-      <c r="B13" s="11" t="s">
+    <row r="81" spans="2:2" ht="15.5">
+      <c r="B81" s="11" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="15.5">
-      <c r="B14" s="11" t="s">
+    <row r="82" spans="2:2" ht="15.5">
+      <c r="B82" s="11" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="15.5">
-      <c r="B15" s="11" t="s">
+    <row r="83" spans="2:2" ht="15.5">
+      <c r="B83" s="11" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="15.5">
-      <c r="B16" s="11" t="s">
+    <row r="84" spans="2:2" ht="15.5">
+      <c r="B84" s="11" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="15.5">
-      <c r="B17" s="11" t="s">
+    <row r="85" spans="2:2" ht="15.5">
+      <c r="B85" s="11" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="15.5">
-      <c r="B18" s="11" t="s">
+    <row r="86" spans="2:2" ht="15.5">
+      <c r="B86" s="11" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="15.5">
-      <c r="B19" s="11" t="s">
+    <row r="87" spans="2:2" ht="15.5">
+      <c r="B87" s="11" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="15.5">
-      <c r="B20" s="11" t="s">
+    <row r="88" spans="2:2" ht="15.5">
+      <c r="B88" s="11" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="15.5">
-      <c r="B21" s="11" t="s">
+    <row r="89" spans="2:2" ht="15.5">
+      <c r="B89" s="11" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="15.5">
-      <c r="B22" s="11" t="s">
+    <row r="90" spans="2:2" ht="15.5">
+      <c r="B90" s="11" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="15.5">
-      <c r="B23" s="11" t="s">
+    <row r="91" spans="2:2" ht="15.5">
+      <c r="B91" s="11" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="15.5">
-      <c r="B24" s="11" t="s">
+    <row r="92" spans="2:2" ht="15.5">
+      <c r="B92" s="11" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="15.5">
-      <c r="B25" s="11" t="s">
+    <row r="93" spans="2:2" ht="15.5">
+      <c r="B93" s="11" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="15.5">
-      <c r="B26" s="11" t="s">
+    <row r="94" spans="2:2" ht="15.5">
+      <c r="B94" s="11" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="15.5">
-      <c r="B27" s="11" t="s">
+    <row r="95" spans="2:2" ht="15.5">
+      <c r="B95" s="11" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="15.5">
-      <c r="B28" s="11" t="s">
+    <row r="96" spans="2:2" ht="15.5">
+      <c r="B96" s="11" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="15.5">
-      <c r="B29" s="11" t="s">
+    <row r="97" spans="2:2" ht="15.5">
+      <c r="B97" s="11" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="15.5">
-      <c r="B30" s="11" t="s">
+    <row r="98" spans="2:2" ht="15.5">
+      <c r="B98" s="11" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="15.5">
-      <c r="B31" s="11" t="s">
+    <row r="99" spans="2:2" ht="15.5">
+      <c r="B99" s="11" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="15.5">
-      <c r="B32" s="11" t="s">
+    <row r="100" spans="2:2" ht="15.5">
+      <c r="B100" s="11" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="15.5">
-      <c r="B33" s="11" t="s">
+    <row r="101" spans="2:2" ht="15.5">
+      <c r="B101" s="11" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="15.5">
-      <c r="B34" s="11" t="s">
+    <row r="102" spans="2:2" ht="15.5">
+      <c r="B102" s="11" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="15.5">
-      <c r="B35" s="11" t="s">
+    <row r="103" spans="2:2" ht="15.5">
+      <c r="B103" s="11" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="15.5">
-      <c r="B36" s="11" t="s">
+    <row r="104" spans="2:2" ht="15.5">
+      <c r="B104" s="11" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="15.5">
-      <c r="B37" s="11" t="s">
+    <row r="105" spans="2:2" ht="15.5">
+      <c r="B105" s="11" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="15.5">
-      <c r="B38" s="11" t="s">
+    <row r="106" spans="2:2" ht="15.5">
+      <c r="B106" s="11" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="39" spans="2:2" ht="15.5">
-      <c r="B39" s="11" t="s">
+    <row r="107" spans="2:2" ht="15.5">
+      <c r="B107" s="11" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="40" spans="2:2" ht="15.5">
-      <c r="B40" s="11" t="s">
+    <row r="108" spans="2:2" ht="15.5">
+      <c r="B108" s="11" t="s">
         <v>393</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9461,7 +10785,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="B2:D25"/>
+  <dimension ref="B2:J32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -9479,9 +10803,14 @@
         <v>399</v>
       </c>
     </row>
-    <row r="25" spans="4:4">
+    <row r="25" spans="4:10">
       <c r="D25" t="s">
         <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="4:10">
+      <c r="J32" t="s">
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/IT授業内容(智源).xlsx
+++ b/IT授業内容(智源).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tech\git20220205\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF2DC00-519E-49C8-838D-035D338476C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B703C16-7AA0-41D5-B0CC-0D5EA51DCCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4150" yWindow="2460" windowWidth="16160" windowHeight="5660" tabRatio="809" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必要ツール" sheetId="3" r:id="rId1"/>
@@ -24,12 +24,13 @@
     <sheet name="SQL宿題1" sheetId="6" r:id="rId9"/>
     <sheet name="SQL宿題2" sheetId="16" r:id="rId10"/>
     <sheet name="JVM里变量加载图" sheetId="18" r:id="rId11"/>
-    <sheet name="１" sheetId="9" state="hidden" r:id="rId12"/>
-    <sheet name="2" sheetId="10" state="hidden" r:id="rId13"/>
-    <sheet name="３" sheetId="11" state="hidden" r:id="rId14"/>
-    <sheet name="４" sheetId="12" state="hidden" r:id="rId15"/>
-    <sheet name="５" sheetId="13" state="hidden" r:id="rId16"/>
-    <sheet name="6" sheetId="14" state="hidden" r:id="rId17"/>
+    <sheet name="windowbuilder安装" sheetId="19" r:id="rId12"/>
+    <sheet name="１" sheetId="9" state="hidden" r:id="rId13"/>
+    <sheet name="2" sheetId="10" state="hidden" r:id="rId14"/>
+    <sheet name="３" sheetId="11" state="hidden" r:id="rId15"/>
+    <sheet name="４" sheetId="12" state="hidden" r:id="rId16"/>
+    <sheet name="５" sheetId="13" state="hidden" r:id="rId17"/>
+    <sheet name="6" sheetId="14" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'ITフレームワーク(４～６ケ月)'!$A$1:$H$38</definedName>
@@ -465,7 +466,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="564">
   <si>
     <t>日付</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2704,6 +2705,34 @@
     <t>TreeMap</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>https://download.eclipse.org/windowbuilder/latest/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sc delete mysql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="NSimSun"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="22"/>
+  </si>
 </sst>
 </file>
 
@@ -2712,7 +2741,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;月&quot;dd&quot;日&quot;\(aaa\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2853,8 +2882,28 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="NSimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2906,6 +2955,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3282,7 +3337,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -3361,51 +3416,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3461,6 +3471,54 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3826,6 +3884,402 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>494809</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>2790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B80AD992-BCCC-4D65-BC8E-F601F81D930B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="177800"/>
+          <a:ext cx="3796809" cy="2314190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>542086</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>75833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11D5AC8-1225-45F9-B593-FB9B51EFCF24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="2667000"/>
+          <a:ext cx="6485686" cy="2209433"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342343</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>142113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F83D79C-7571-4824-8547-DE5BD4F0ECFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="4978400"/>
+          <a:ext cx="4304743" cy="4587113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>466417</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>85573</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A18A6A0-A5AB-4DEE-994B-B3AAB292F912}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="717550" y="13036550"/>
+          <a:ext cx="2390467" cy="917423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>173</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>170743</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>177295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{492293ED-53C7-4B30-A332-AF955DD83CC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="9779000"/>
+          <a:ext cx="5453943" cy="3022095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>370486</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>123482</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DB6624A-D7FB-43AB-A513-2D04E923C90E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="15290800"/>
+          <a:ext cx="7634886" cy="2079282"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>399315</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>152249</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB686334-1E55-42DC-9348-46F8F4EC1336}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="669925" y="14179550"/>
+          <a:ext cx="5672990" cy="907899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123295</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>123393</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C4019BE-A62F-4ACA-B920-7CFD98192217}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="17602200"/>
+          <a:ext cx="4085695" cy="2612593"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>237495</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>123542</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EA6356C-2E19-450E-9F19-3DCA922EAC39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="20269200"/>
+          <a:ext cx="4860295" cy="1723742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5402,26 +5856,26 @@
     </row>
     <row r="3" spans="2:4">
       <c r="B3" s="44">
-        <f>ROW()-2</f>
+        <f t="shared" ref="B3:B14" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="44">
-        <f t="shared" ref="B4:B14" si="0">ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>513</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="2:4">
@@ -5430,10 +5884,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>513</v>
+        <v>25</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -5442,10 +5896,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -5454,10 +5908,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>509</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>508</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="2:4">
@@ -5466,10 +5920,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>509</v>
+        <v>19</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -5478,10 +5932,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -5490,22 +5944,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>529</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="44">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>529</v>
+        <v>18</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" spans="2:4">
@@ -5545,14 +5999,14 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{723AFD1C-B9A4-4386-89E0-F419B5DD451A}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{22AEB766-92F6-470E-8207-79A0C64B1CF8}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{2009036F-2C07-49EF-85D8-F94C1CBB5BD2}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{1A5FFFE6-4967-4225-9B2C-3F0BCFF3D5FE}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{32B20C4C-7BFD-48DC-BB0A-BC6915508E6F}"/>
-    <hyperlink ref="D10" r:id="rId6" xr:uid="{204584A2-B173-4E3E-8317-F0E215C42A19}"/>
-    <hyperlink ref="D5" r:id="rId7" xr:uid="{4FA2EA2B-CC81-41A0-9980-C94CAE5CEF6B}"/>
-    <hyperlink ref="D11" r:id="rId8" xr:uid="{2C15FE46-DE0D-4EB9-8911-16F8C2AD9C51}"/>
+    <hyperlink ref="D11" r:id="rId1" xr:uid="{723AFD1C-B9A4-4386-89E0-F419B5DD451A}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{22AEB766-92F6-470E-8207-79A0C64B1CF8}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{2009036F-2C07-49EF-85D8-F94C1CBB5BD2}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{1A5FFFE6-4967-4225-9B2C-3F0BCFF3D5FE}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{32B20C4C-7BFD-48DC-BB0A-BC6915508E6F}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{204584A2-B173-4E3E-8317-F0E215C42A19}"/>
+    <hyperlink ref="D4" r:id="rId7" xr:uid="{4FA2EA2B-CC81-41A0-9980-C94CAE5CEF6B}"/>
+    <hyperlink ref="D10" r:id="rId8" xr:uid="{2C15FE46-DE0D-4EB9-8911-16F8C2AD9C51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -6092,644 +6546,644 @@
   <dimension ref="C2:Z27"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="20" width="8.6640625" style="67"/>
-    <col min="21" max="26" width="8.6640625" style="89"/>
-    <col min="27" max="16384" width="8.6640625" style="67"/>
+    <col min="1" max="20" width="8.6640625" style="52"/>
+    <col min="21" max="26" width="8.6640625" style="74"/>
+    <col min="27" max="16384" width="8.6640625" style="52"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:26">
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="52" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="3" spans="3:26">
-      <c r="U3" s="90"/>
-      <c r="V3" s="90"/>
-      <c r="W3" s="90"/>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="75"/>
+      <c r="Y3" s="75"/>
     </row>
     <row r="4" spans="3:26">
-      <c r="U4" s="90">
+      <c r="U4" s="75">
         <v>1</v>
       </c>
-      <c r="V4" s="90"/>
-      <c r="W4" s="90">
+      <c r="V4" s="75"/>
+      <c r="W4" s="75">
         <v>2</v>
       </c>
-      <c r="X4" s="90"/>
-      <c r="Y4" s="90">
+      <c r="X4" s="75"/>
+      <c r="Y4" s="75">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="3:26">
-      <c r="U5" s="90" t="s">
+      <c r="U5" s="75" t="s">
         <v>550</v>
       </c>
-      <c r="V5" s="90" t="s">
+      <c r="V5" s="75" t="s">
         <v>551</v>
       </c>
-      <c r="W5" s="90" t="s">
+      <c r="W5" s="75" t="s">
         <v>552</v>
       </c>
-      <c r="X5" s="90" t="s">
+      <c r="X5" s="75" t="s">
         <v>551</v>
       </c>
-      <c r="Y5" s="90" t="s">
+      <c r="Y5" s="75" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="14.5" thickBot="1"/>
     <row r="7" spans="3:26">
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="69"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="69"/>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="92"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="76"/>
+      <c r="V7" s="76"/>
+      <c r="W7" s="76"/>
+      <c r="X7" s="76"/>
+      <c r="Y7" s="76"/>
+      <c r="Z7" s="77"/>
     </row>
     <row r="8" spans="3:26" ht="14.5" thickBot="1">
-      <c r="C8" s="71"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72" t="s">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57" t="s">
         <v>554</v>
       </c>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72" t="s">
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57" t="s">
         <v>556</v>
       </c>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="93"/>
-      <c r="V8" s="93"/>
-      <c r="W8" s="93" t="s">
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="78"/>
+      <c r="V8" s="78"/>
+      <c r="W8" s="78" t="s">
         <v>557</v>
       </c>
-      <c r="X8" s="93"/>
-      <c r="Y8" s="93"/>
-      <c r="Z8" s="94"/>
+      <c r="X8" s="78"/>
+      <c r="Y8" s="78"/>
+      <c r="Z8" s="79"/>
     </row>
     <row r="9" spans="3:26">
-      <c r="C9" s="71"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="77" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="62" t="s">
         <v>555</v>
       </c>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="79"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="92"/>
-      <c r="V9" s="93"/>
-      <c r="W9" s="97"/>
-      <c r="X9" s="91"/>
-      <c r="Y9" s="92"/>
-      <c r="Z9" s="94"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="77"/>
+      <c r="V9" s="78"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="77"/>
+      <c r="Z9" s="79"/>
     </row>
     <row r="10" spans="3:26" ht="14.5" thickBot="1">
-      <c r="C10" s="71"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="94"/>
-      <c r="V10" s="93"/>
-      <c r="W10" s="98"/>
-      <c r="X10" s="93"/>
-      <c r="Y10" s="94"/>
-      <c r="Z10" s="94"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="78"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="78"/>
+      <c r="Y10" s="79"/>
+      <c r="Z10" s="79"/>
     </row>
     <row r="11" spans="3:26">
-      <c r="C11" s="71"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="83" t="s">
+      <c r="C11" s="56"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="H11" s="83" t="s">
+      <c r="H11" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="I11" s="83" t="s">
+      <c r="I11" s="68" t="s">
         <v>547</v>
       </c>
-      <c r="J11" s="83" t="s">
+      <c r="J11" s="68" t="s">
         <v>545</v>
       </c>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="94"/>
-      <c r="V11" s="93"/>
-      <c r="W11" s="98"/>
-      <c r="X11" s="93"/>
-      <c r="Y11" s="94"/>
-      <c r="Z11" s="94"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="79"/>
+      <c r="V11" s="78"/>
+      <c r="W11" s="83"/>
+      <c r="X11" s="78"/>
+      <c r="Y11" s="79"/>
+      <c r="Z11" s="79"/>
     </row>
     <row r="12" spans="3:26">
-      <c r="C12" s="71"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="94"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="94"/>
-      <c r="Z12" s="94"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="78"/>
+      <c r="W12" s="83"/>
+      <c r="X12" s="78"/>
+      <c r="Y12" s="79"/>
+      <c r="Z12" s="79"/>
     </row>
     <row r="13" spans="3:26">
-      <c r="C13" s="71"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84" t="s">
+      <c r="C13" s="56"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69" t="s">
         <v>548</v>
       </c>
-      <c r="J13" s="84" t="s">
+      <c r="J13" s="69" t="s">
         <v>546</v>
       </c>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="94"/>
-      <c r="V13" s="93"/>
-      <c r="W13" s="98"/>
-      <c r="X13" s="93"/>
-      <c r="Y13" s="94"/>
-      <c r="Z13" s="94"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="79"/>
+      <c r="V13" s="78"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="78"/>
+      <c r="Y13" s="79"/>
+      <c r="Z13" s="79"/>
     </row>
     <row r="14" spans="3:26">
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69" t="s">
         <v>549</v>
       </c>
-      <c r="J14" s="84"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="82"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="94"/>
-      <c r="V14" s="93"/>
-      <c r="W14" s="98"/>
-      <c r="X14" s="93"/>
-      <c r="Y14" s="94"/>
-      <c r="Z14" s="94"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="79"/>
+      <c r="V14" s="78"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="78"/>
+      <c r="Y14" s="79"/>
+      <c r="Z14" s="79"/>
     </row>
     <row r="15" spans="3:26">
-      <c r="C15" s="71"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="94"/>
-      <c r="V15" s="93"/>
-      <c r="W15" s="98"/>
-      <c r="X15" s="93"/>
-      <c r="Y15" s="94"/>
-      <c r="Z15" s="94"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="79"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="83"/>
+      <c r="X15" s="78"/>
+      <c r="Y15" s="79"/>
+      <c r="Z15" s="79"/>
     </row>
     <row r="16" spans="3:26" ht="14.5" thickBot="1">
-      <c r="C16" s="71"/>
-      <c r="D16" s="72" t="s">
+      <c r="C16" s="56"/>
+      <c r="D16" s="57" t="s">
         <v>558</v>
       </c>
-      <c r="E16" s="73"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="85"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="86"/>
-      <c r="N16" s="86"/>
-      <c r="O16" s="87"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="94"/>
-      <c r="V16" s="93"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="93"/>
-      <c r="Y16" s="94"/>
-      <c r="Z16" s="94"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="79"/>
+      <c r="V16" s="78"/>
+      <c r="W16" s="83"/>
+      <c r="X16" s="78"/>
+      <c r="Y16" s="79"/>
+      <c r="Z16" s="79"/>
     </row>
     <row r="17" spans="3:26" ht="14.5" thickBot="1">
-      <c r="C17" s="71"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="86"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="86"/>
-      <c r="N17" s="86"/>
-      <c r="O17" s="86"/>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="94"/>
-      <c r="V17" s="93"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="93"/>
-      <c r="Y17" s="94"/>
-      <c r="Z17" s="94"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="79"/>
+      <c r="V17" s="78"/>
+      <c r="W17" s="83"/>
+      <c r="X17" s="78"/>
+      <c r="Y17" s="79"/>
+      <c r="Z17" s="79"/>
     </row>
     <row r="18" spans="3:26">
-      <c r="C18" s="71"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="71" t="s">
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="56" t="s">
         <v>532</v>
       </c>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="68" t="s">
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="53" t="s">
         <v>533</v>
       </c>
-      <c r="K18" s="69"/>
-      <c r="L18" s="69"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
-      <c r="U18" s="94"/>
-      <c r="V18" s="93"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="93"/>
-      <c r="Y18" s="94"/>
-      <c r="Z18" s="94"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="79"/>
+      <c r="V18" s="78"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="78"/>
+      <c r="Y18" s="79"/>
+      <c r="Z18" s="79"/>
     </row>
     <row r="19" spans="3:26">
-      <c r="C19" s="71"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="71" t="s">
+      <c r="C19" s="56"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="56" t="s">
         <v>534</v>
       </c>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="72" t="s">
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="57" t="s">
         <v>542</v>
       </c>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="93"/>
-      <c r="W19" s="98"/>
-      <c r="X19" s="93"/>
-      <c r="Y19" s="94"/>
-      <c r="Z19" s="94"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="79"/>
+      <c r="V19" s="78"/>
+      <c r="W19" s="83"/>
+      <c r="X19" s="78"/>
+      <c r="Y19" s="79"/>
+      <c r="Z19" s="79"/>
     </row>
     <row r="20" spans="3:26">
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="71" t="s">
+      <c r="C20" s="56"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="56" t="s">
         <v>535</v>
       </c>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
-      <c r="U20" s="94"/>
-      <c r="V20" s="93"/>
-      <c r="W20" s="98"/>
-      <c r="X20" s="93"/>
-      <c r="Y20" s="94"/>
-      <c r="Z20" s="94"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="56"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="79"/>
+      <c r="V20" s="78"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="78"/>
+      <c r="Y20" s="79"/>
+      <c r="Z20" s="79"/>
     </row>
     <row r="21" spans="3:26">
-      <c r="C21" s="71"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="71" t="s">
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="56" t="s">
         <v>536</v>
       </c>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="94"/>
-      <c r="V21" s="93"/>
-      <c r="W21" s="98"/>
-      <c r="X21" s="93"/>
-      <c r="Y21" s="94"/>
-      <c r="Z21" s="94"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="78"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="78"/>
+      <c r="Y21" s="79"/>
+      <c r="Z21" s="79"/>
     </row>
     <row r="22" spans="3:26">
-      <c r="C22" s="71"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="71" t="s">
+      <c r="C22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="56" t="s">
         <v>537</v>
       </c>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="72"/>
-      <c r="T22" s="72"/>
-      <c r="U22" s="94"/>
-      <c r="V22" s="93"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="93"/>
-      <c r="Y22" s="94"/>
-      <c r="Z22" s="94"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="79"/>
+      <c r="V22" s="78"/>
+      <c r="W22" s="83"/>
+      <c r="X22" s="78"/>
+      <c r="Y22" s="79"/>
+      <c r="Z22" s="79"/>
     </row>
     <row r="23" spans="3:26">
-      <c r="C23" s="71"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="71" t="s">
+      <c r="C23" s="56"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="56" t="s">
         <v>538</v>
       </c>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="94"/>
-      <c r="V23" s="93"/>
-      <c r="W23" s="98"/>
-      <c r="X23" s="93"/>
-      <c r="Y23" s="94"/>
-      <c r="Z23" s="94"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="56"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="79"/>
+      <c r="V23" s="78"/>
+      <c r="W23" s="83"/>
+      <c r="X23" s="78"/>
+      <c r="Y23" s="79"/>
+      <c r="Z23" s="79"/>
     </row>
     <row r="24" spans="3:26">
-      <c r="C24" s="71"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="71" t="s">
+      <c r="C24" s="56"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="56" t="s">
         <v>539</v>
       </c>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="72"/>
-      <c r="T24" s="72"/>
-      <c r="U24" s="94"/>
-      <c r="V24" s="93"/>
-      <c r="W24" s="98"/>
-      <c r="X24" s="93"/>
-      <c r="Y24" s="94"/>
-      <c r="Z24" s="94"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="56"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="79"/>
+      <c r="V24" s="78"/>
+      <c r="W24" s="83"/>
+      <c r="X24" s="78"/>
+      <c r="Y24" s="79"/>
+      <c r="Z24" s="79"/>
     </row>
     <row r="25" spans="3:26">
-      <c r="C25" s="71"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="71" t="s">
+      <c r="C25" s="56"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="56" t="s">
         <v>540</v>
       </c>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="72"/>
-      <c r="T25" s="72"/>
-      <c r="U25" s="94"/>
-      <c r="V25" s="93"/>
-      <c r="W25" s="98"/>
-      <c r="X25" s="93"/>
-      <c r="Y25" s="94"/>
-      <c r="Z25" s="94"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="56"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="79"/>
+      <c r="V25" s="78"/>
+      <c r="W25" s="83"/>
+      <c r="X25" s="78"/>
+      <c r="Y25" s="79"/>
+      <c r="Z25" s="79"/>
     </row>
     <row r="26" spans="3:26" ht="14.5" thickBot="1">
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="C26" s="56"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
         <v>541</v>
       </c>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="76"/>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="96"/>
-      <c r="V26" s="93"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="95"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="94"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="59"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="81"/>
+      <c r="V26" s="78"/>
+      <c r="W26" s="84"/>
+      <c r="X26" s="80"/>
+      <c r="Y26" s="81"/>
+      <c r="Z26" s="79"/>
     </row>
     <row r="27" spans="3:26" ht="14.5" thickBot="1">
-      <c r="C27" s="74"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="75"/>
-      <c r="N27" s="75"/>
-      <c r="O27" s="75"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="95"/>
-      <c r="V27" s="95"/>
-      <c r="W27" s="95"/>
-      <c r="X27" s="95"/>
-      <c r="Y27" s="95"/>
-      <c r="Z27" s="96"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="80"/>
+      <c r="V27" s="80"/>
+      <c r="W27" s="80"/>
+      <c r="X27" s="80"/>
+      <c r="Y27" s="80"/>
+      <c r="Z27" s="81"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6739,6 +7193,29 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41AFFA43-4820-4AD6-9E6A-7F8B8CFA34B7}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="C3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="3" spans="3:3">
+      <c r="C3" s="42" t="s">
+        <v>560</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{219FDB92-7956-47B3-97A5-5BEC17E4A6CC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF30867F-4987-428B-B1BA-79BEE1AC7E24}">
   <dimension ref="B1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6809,7 +7286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D3055-B4C0-44F8-BC38-3332800489E4}">
   <dimension ref="B1:S32"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6984,7 +7461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBA7452-ADCF-4916-B20B-0512AE3ED3F2}">
   <dimension ref="B1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7053,7 +7530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A228C4-8BB0-42F2-86E2-63F3E8493370}">
   <dimension ref="B1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7114,7 +7591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C125254-9191-4F9A-8C38-B14BF103FA27}">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7169,7 +7646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E4EC444-DA0C-43AC-8DA7-D83AAF18CFD5}">
   <dimension ref="B1:S26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7438,7 +7915,7 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="85" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6">
@@ -7457,7 +7934,7 @@
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="89" t="s">
         <v>14</v>
       </c>
       <c r="J3" s="33">
@@ -7465,7 +7942,7 @@
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="53"/>
+      <c r="B4" s="86"/>
       <c r="C4" s="6">
         <f>$J$3</f>
         <v>44598</v>
@@ -7482,10 +7959,10 @@
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="57"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="53"/>
+      <c r="B5" s="86"/>
       <c r="C5" s="6">
         <f>$J$3</f>
         <v>44598</v>
@@ -7502,10 +7979,10 @@
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="57"/>
+      <c r="H5" s="90"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="53"/>
+      <c r="B6" s="86"/>
       <c r="C6" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -7522,12 +7999,12 @@
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="89" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="53"/>
+      <c r="B7" s="86"/>
       <c r="C7" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -7544,10 +8021,10 @@
       <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="57"/>
+      <c r="H7" s="90"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="53"/>
+      <c r="B8" s="86"/>
       <c r="C8" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -7564,10 +8041,10 @@
       <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="57"/>
+      <c r="H8" s="90"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="53"/>
+      <c r="B9" s="86"/>
       <c r="C9" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -7584,12 +8061,12 @@
       <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="90" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="53"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -7606,10 +8083,10 @@
       <c r="G10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="57"/>
+      <c r="H10" s="90"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="53"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -7626,10 +8103,10 @@
       <c r="G11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="57"/>
+      <c r="H11" s="90"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="53"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="6">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -7646,12 +8123,12 @@
       <c r="G12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="56" t="s">
+      <c r="H12" s="89" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="53"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="6">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -7668,10 +8145,10 @@
       <c r="G13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="57"/>
+      <c r="H13" s="90"/>
     </row>
     <row r="14" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B14" s="54"/>
+      <c r="B14" s="87"/>
       <c r="C14" s="28">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -7688,10 +8165,10 @@
       <c r="G14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="91"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="88" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="29">
@@ -7710,7 +8187,7 @@
       <c r="G15" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="H15" s="59" t="s">
+      <c r="H15" s="92" t="s">
         <v>42</v>
       </c>
       <c r="J15" s="33">
@@ -7718,7 +8195,7 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="53"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="6">
         <f>$J$15</f>
         <v>44626</v>
@@ -7735,10 +8212,10 @@
       <c r="G16" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="H16" s="57"/>
+      <c r="H16" s="90"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="53"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="6">
         <f>$J$15</f>
         <v>44626</v>
@@ -7755,10 +8232,10 @@
       <c r="G17" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H17" s="57"/>
+      <c r="H17" s="90"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="53"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -7775,12 +8252,12 @@
       <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="60" t="s">
+      <c r="H18" s="93" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="53"/>
+      <c r="B19" s="86"/>
       <c r="C19" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -7797,10 +8274,10 @@
       <c r="G19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="57"/>
+      <c r="H19" s="90"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="53"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -7817,10 +8294,10 @@
       <c r="G20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="57"/>
+      <c r="H20" s="90"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="53"/>
+      <c r="B21" s="86"/>
       <c r="C21" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -7837,12 +8314,12 @@
       <c r="G21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H21" s="90" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="53"/>
+      <c r="B22" s="86"/>
       <c r="C22" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -7859,10 +8336,10 @@
       <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="57"/>
+      <c r="H22" s="90"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="53"/>
+      <c r="B23" s="86"/>
       <c r="C23" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -7879,10 +8356,10 @@
       <c r="G23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="57"/>
+      <c r="H23" s="90"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="53"/>
+      <c r="B24" s="86"/>
       <c r="C24" s="6">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -7899,12 +8376,12 @@
       <c r="G24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="57" t="s">
+      <c r="H24" s="90" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="53"/>
+      <c r="B25" s="86"/>
       <c r="C25" s="6">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -7921,10 +8398,10 @@
       <c r="G25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="57"/>
+      <c r="H25" s="90"/>
     </row>
     <row r="26" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B26" s="54"/>
+      <c r="B26" s="87"/>
       <c r="C26" s="30">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -7941,10 +8418,10 @@
       <c r="G26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="61"/>
+      <c r="H26" s="94"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="88" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="31">
@@ -7963,7 +8440,7 @@
       <c r="G27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="62" t="s">
+      <c r="H27" s="95" t="s">
         <v>480</v>
       </c>
       <c r="J27" s="33">
@@ -7971,7 +8448,7 @@
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="53"/>
+      <c r="B28" s="86"/>
       <c r="C28" s="6">
         <f>$J$27</f>
         <v>44654</v>
@@ -7988,10 +8465,10 @@
       <c r="G28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="57"/>
+      <c r="H28" s="90"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="53"/>
+      <c r="B29" s="86"/>
       <c r="C29" s="6">
         <f>$J$27</f>
         <v>44654</v>
@@ -8008,10 +8485,10 @@
       <c r="G29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="57"/>
+      <c r="H29" s="90"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="53"/>
+      <c r="B30" s="86"/>
       <c r="C30" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -8028,12 +8505,12 @@
       <c r="G30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="90" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="53"/>
+      <c r="B31" s="86"/>
       <c r="C31" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -8050,10 +8527,10 @@
       <c r="G31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H31" s="57"/>
+      <c r="H31" s="90"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="53"/>
+      <c r="B32" s="86"/>
       <c r="C32" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -8070,10 +8547,10 @@
       <c r="G32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H32" s="57"/>
+      <c r="H32" s="90"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="53"/>
+      <c r="B33" s="86"/>
       <c r="C33" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -8090,12 +8567,12 @@
       <c r="G33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="56" t="s">
+      <c r="H33" s="89" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="53"/>
+      <c r="B34" s="86"/>
       <c r="C34" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -8112,10 +8589,10 @@
       <c r="G34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H34" s="57"/>
+      <c r="H34" s="90"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="53"/>
+      <c r="B35" s="86"/>
       <c r="C35" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -8132,10 +8609,10 @@
       <c r="G35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H35" s="57"/>
+      <c r="H35" s="90"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="53"/>
+      <c r="B36" s="86"/>
       <c r="C36" s="6">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -8152,12 +8629,12 @@
       <c r="G36" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="H36" s="56" t="s">
+      <c r="H36" s="89" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="53"/>
+      <c r="B37" s="86"/>
       <c r="C37" s="6">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -8174,10 +8651,10 @@
       <c r="G37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="57"/>
+      <c r="H37" s="90"/>
     </row>
     <row r="38" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B38" s="54"/>
+      <c r="B38" s="87"/>
       <c r="C38" s="28">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -8194,7 +8671,7 @@
       <c r="G38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="58"/>
+      <c r="H38" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -8265,7 +8742,7 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="85" t="s">
         <v>490</v>
       </c>
       <c r="C3" s="6">
@@ -8284,7 +8761,7 @@
       <c r="G3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="89" t="s">
         <v>517</v>
       </c>
       <c r="J3" s="33">
@@ -8292,7 +8769,7 @@
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="63"/>
+      <c r="B4" s="96"/>
       <c r="C4" s="6">
         <f>$J$3</f>
         <v>44689</v>
@@ -8309,10 +8786,10 @@
       <c r="G4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="57"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="63"/>
+      <c r="B5" s="96"/>
       <c r="C5" s="6">
         <f>$J$3</f>
         <v>44689</v>
@@ -8329,10 +8806,10 @@
       <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="57"/>
+      <c r="H5" s="90"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="63"/>
+      <c r="B6" s="96"/>
       <c r="C6" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -8349,12 +8826,12 @@
       <c r="G6" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="89" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="63"/>
+      <c r="B7" s="96"/>
       <c r="C7" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -8371,10 +8848,10 @@
       <c r="G7" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="H7" s="57"/>
+      <c r="H7" s="90"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="63"/>
+      <c r="B8" s="96"/>
       <c r="C8" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -8391,10 +8868,10 @@
       <c r="G8" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="H8" s="57"/>
+      <c r="H8" s="90"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="63"/>
+      <c r="B9" s="96"/>
       <c r="C9" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -8411,10 +8888,10 @@
       <c r="G9" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H9" s="57"/>
+      <c r="H9" s="90"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="63"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -8431,10 +8908,10 @@
       <c r="G10" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H10" s="57"/>
+      <c r="H10" s="90"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="63"/>
+      <c r="B11" s="96"/>
       <c r="C11" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -8451,10 +8928,10 @@
       <c r="G11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="57"/>
+      <c r="H11" s="90"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="63"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="6">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -8471,10 +8948,10 @@
       <c r="G12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="57"/>
+      <c r="H12" s="90"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="63"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="6">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -8491,10 +8968,10 @@
       <c r="G13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="57"/>
+      <c r="H13" s="90"/>
     </row>
     <row r="14" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B14" s="63"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="28">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -8511,10 +8988,10 @@
       <c r="G14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="91"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="63"/>
+      <c r="B15" s="96"/>
       <c r="C15" s="29">
         <f>$J$15</f>
         <v>44717</v>
@@ -8531,13 +9008,13 @@
       <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="66"/>
+      <c r="H15" s="99"/>
       <c r="J15" s="33">
         <v>44717</v>
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="63"/>
+      <c r="B16" s="96"/>
       <c r="C16" s="6">
         <f>$J$15</f>
         <v>44717</v>
@@ -8554,10 +9031,10 @@
       <c r="G16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="57"/>
+      <c r="H16" s="90"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="63"/>
+      <c r="B17" s="96"/>
       <c r="C17" s="6">
         <f>$J$15</f>
         <v>44717</v>
@@ -8574,10 +9051,10 @@
       <c r="G17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="57"/>
+      <c r="H17" s="90"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="63"/>
+      <c r="B18" s="96"/>
       <c r="C18" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -8594,10 +9071,10 @@
       <c r="G18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="57"/>
+      <c r="H18" s="90"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="63"/>
+      <c r="B19" s="96"/>
       <c r="C19" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -8614,10 +9091,10 @@
       <c r="G19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="57"/>
+      <c r="H19" s="90"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="63"/>
+      <c r="B20" s="96"/>
       <c r="C20" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -8634,10 +9111,10 @@
       <c r="G20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="57"/>
+      <c r="H20" s="90"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="63"/>
+      <c r="B21" s="96"/>
       <c r="C21" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -8654,10 +9131,10 @@
       <c r="G21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="57"/>
+      <c r="H21" s="90"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="63"/>
+      <c r="B22" s="96"/>
       <c r="C22" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -8674,10 +9151,10 @@
       <c r="G22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="57"/>
+      <c r="H22" s="90"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="63"/>
+      <c r="B23" s="96"/>
       <c r="C23" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -8694,10 +9171,10 @@
       <c r="G23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="57"/>
+      <c r="H23" s="90"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="63"/>
+      <c r="B24" s="96"/>
       <c r="C24" s="6">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -8714,10 +9191,10 @@
       <c r="G24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="57"/>
+      <c r="H24" s="90"/>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="63"/>
+      <c r="B25" s="96"/>
       <c r="C25" s="6">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -8734,10 +9211,10 @@
       <c r="G25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="57"/>
+      <c r="H25" s="90"/>
     </row>
     <row r="26" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B26" s="64"/>
+      <c r="B26" s="97"/>
       <c r="C26" s="30">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -8754,10 +9231,10 @@
       <c r="G26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="61"/>
+      <c r="H26" s="94"/>
     </row>
     <row r="27" spans="2:10" ht="14" customHeight="1">
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="98" t="s">
         <v>489</v>
       </c>
       <c r="C27" s="31">
@@ -8776,7 +9253,7 @@
       <c r="G27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="62" t="s">
+      <c r="H27" s="95" t="s">
         <v>518</v>
       </c>
       <c r="J27" s="33">
@@ -8784,7 +9261,7 @@
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="63"/>
+      <c r="B28" s="96"/>
       <c r="C28" s="6">
         <f>$J$27</f>
         <v>44745</v>
@@ -8801,10 +9278,10 @@
       <c r="G28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="57"/>
+      <c r="H28" s="90"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="63"/>
+      <c r="B29" s="96"/>
       <c r="C29" s="6">
         <f>$J$27</f>
         <v>44745</v>
@@ -8821,10 +9298,10 @@
       <c r="G29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="57"/>
+      <c r="H29" s="90"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="63"/>
+      <c r="B30" s="96"/>
       <c r="C30" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -8841,12 +9318,12 @@
       <c r="G30" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="90" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="63"/>
+      <c r="B31" s="96"/>
       <c r="C31" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -8863,10 +9340,10 @@
       <c r="G31" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="H31" s="57"/>
+      <c r="H31" s="90"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="63"/>
+      <c r="B32" s="96"/>
       <c r="C32" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -8883,10 +9360,10 @@
       <c r="G32" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="H32" s="57"/>
+      <c r="H32" s="90"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="96" t="s">
         <v>527</v>
       </c>
       <c r="C33" s="6">
@@ -8905,10 +9382,10 @@
       <c r="G33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="57"/>
+      <c r="H33" s="90"/>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="63"/>
+      <c r="B34" s="96"/>
       <c r="C34" s="6">
         <f>$J$27+14</f>
         <v>44759</v>
@@ -8925,10 +9402,10 @@
       <c r="G34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="57"/>
+      <c r="H34" s="90"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="63"/>
+      <c r="B35" s="96"/>
       <c r="C35" s="6">
         <f>$J$27+14</f>
         <v>44759</v>
@@ -8945,10 +9422,10 @@
       <c r="G35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H35" s="57"/>
+      <c r="H35" s="90"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="96" t="s">
         <v>528</v>
       </c>
       <c r="C36" s="6">
@@ -8967,10 +9444,10 @@
       <c r="G36" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H36" s="57"/>
+      <c r="H36" s="90"/>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="53"/>
+      <c r="B37" s="86"/>
       <c r="C37" s="6">
         <f>$J$27+21</f>
         <v>44766</v>
@@ -8987,10 +9464,10 @@
       <c r="G37" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="H37" s="57"/>
+      <c r="H37" s="90"/>
     </row>
     <row r="38" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B38" s="54"/>
+      <c r="B38" s="87"/>
       <c r="C38" s="28">
         <f>$J$27+21</f>
         <v>44766</v>
@@ -9007,7 +9484,7 @@
       <c r="G38" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="H38" s="58"/>
+      <c r="H38" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -9042,7 +9519,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B70:B108"/>
+  <dimension ref="A70:B246"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="70" spans="2:2" ht="15.5">
@@ -9235,10 +9712,26 @@
         <v>393</v>
       </c>
     </row>
+    <row r="118" spans="1:1" s="100" customFormat="1">
+      <c r="A118" s="101" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" s="100" customFormat="1">
+      <c r="A244" s="100" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="B246" s="102" t="s">
+        <v>563</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/IT授業内容(智源).xlsx
+++ b/IT授業内容(智源).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tech\git20220205\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B703C16-7AA0-41D5-B0CC-0D5EA51DCCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142CFB3D-3777-4F7D-9E01-310CB312F92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必要ツール" sheetId="3" r:id="rId1"/>
@@ -18,19 +18,21 @@
     <sheet name="IT入門(１～３ケ月)" sheetId="1" r:id="rId3"/>
     <sheet name="ITフレームワーク(４～６ケ月)" sheetId="2" r:id="rId4"/>
     <sheet name="mysql install" sheetId="15" r:id="rId5"/>
-    <sheet name="データ準備" sheetId="7" r:id="rId6"/>
-    <sheet name="SQLメモ" sheetId="5" r:id="rId7"/>
-    <sheet name="JAVA宿題" sheetId="4" r:id="rId8"/>
-    <sheet name="SQL宿題1" sheetId="6" r:id="rId9"/>
-    <sheet name="SQL宿題2" sheetId="16" r:id="rId10"/>
-    <sheet name="JVM里变量加载图" sheetId="18" r:id="rId11"/>
-    <sheet name="windowbuilder安装" sheetId="19" r:id="rId12"/>
-    <sheet name="１" sheetId="9" state="hidden" r:id="rId13"/>
-    <sheet name="2" sheetId="10" state="hidden" r:id="rId14"/>
-    <sheet name="３" sheetId="11" state="hidden" r:id="rId15"/>
-    <sheet name="４" sheetId="12" state="hidden" r:id="rId16"/>
-    <sheet name="５" sheetId="13" state="hidden" r:id="rId17"/>
-    <sheet name="6" sheetId="14" state="hidden" r:id="rId18"/>
+    <sheet name="DB基础" sheetId="21" r:id="rId6"/>
+    <sheet name="DB表" sheetId="20" r:id="rId7"/>
+    <sheet name="データ準備" sheetId="7" r:id="rId8"/>
+    <sheet name="SQLメモ" sheetId="5" r:id="rId9"/>
+    <sheet name="JAVA宿題" sheetId="4" r:id="rId10"/>
+    <sheet name="SQL宿題1" sheetId="6" r:id="rId11"/>
+    <sheet name="SQL宿題2" sheetId="16" r:id="rId12"/>
+    <sheet name="JVM里变量加载图" sheetId="18" r:id="rId13"/>
+    <sheet name="windowbuilder安装" sheetId="19" r:id="rId14"/>
+    <sheet name="１" sheetId="9" state="hidden" r:id="rId15"/>
+    <sheet name="2" sheetId="10" state="hidden" r:id="rId16"/>
+    <sheet name="３" sheetId="11" state="hidden" r:id="rId17"/>
+    <sheet name="４" sheetId="12" state="hidden" r:id="rId18"/>
+    <sheet name="５" sheetId="13" state="hidden" r:id="rId19"/>
+    <sheet name="6" sheetId="14" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'ITフレームワーク(４～６ケ月)'!$A$1:$H$38</definedName>
@@ -466,7 +468,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="644">
   <si>
     <t>日付</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1953,36 +1955,21 @@
     <t>D:\&gt;cd D:\soft\mysql-8.0.16-winx64\bin</t>
   </si>
   <si>
-    <t>D:\soft\mysql-8.0.16-winx64\bin&gt;mysqld --initialize --user=mysql --console</t>
-  </si>
-  <si>
     <t>2019-07-06T12:30:49.602523Z 0 [System] [MY-013169] [Server] D:\soft\mysql-8.0.16-winx64\bin\mysqld.exe (mysqld 8.0.16) initializing of server in progress as process 5436</t>
   </si>
   <si>
-    <t>2019-07-06T12:30:55.638634Z 5 [Note] [MY-010454] [Server] A temporary password is generated for root@localhost: y4jsE?;-!fpj</t>
-  </si>
-  <si>
     <t>2019-07-06T12:30:57.865660Z 0 [System] [MY-013170] [Server] D:\soft\mysql-8.0.16-winx64\bin\mysqld.exe (mysqld 8.0.16) initializing of server has completed</t>
   </si>
   <si>
-    <t>D:\soft\mysql-8.0.16-winx64\bin&gt;mysqld -install</t>
-  </si>
-  <si>
     <t>Service successfully installed.</t>
   </si>
   <si>
-    <t>D:\soft\mysql-8.0.16-winx64\bin&gt;net start mysql</t>
-  </si>
-  <si>
     <t>MySQL サービスを開始します..</t>
   </si>
   <si>
     <t>MySQL サービスは正常に開始されました。</t>
   </si>
   <si>
-    <t>D:\soft\mysql-8.0.16-winx64\bin&gt;mysql -u root -p</t>
-  </si>
-  <si>
     <t>Enter password: ************</t>
   </si>
   <si>
@@ -2010,33 +1997,9 @@
     <t>Type 'help;' or '\h' for help. Type '\c' to clear the current input statement.</t>
   </si>
   <si>
-    <t>mysql&gt; alter user root@localhost identified by '123456'</t>
-  </si>
-  <si>
-    <t>    -&gt; ;</t>
-  </si>
-  <si>
     <t>Query OK, 0 rows affected (0.02 sec)</t>
   </si>
   <si>
-    <t>mysql&gt; exit</t>
-  </si>
-  <si>
-    <t>Bye</t>
-  </si>
-  <si>
-    <t>Enter password: ******</t>
-  </si>
-  <si>
-    <t>Your MySQL connection id is 10</t>
-  </si>
-  <si>
-    <t>Server version: 8.0.16 MySQL Community Server - GPL</t>
-  </si>
-  <si>
-    <t>mysql&gt; create database `mydb` character set utf8;</t>
-  </si>
-  <si>
     <t>Query OK, 1 row affected, 1 warning (0.01 sec)</t>
   </si>
   <si>
@@ -2303,10 +2266,6 @@
   </si>
   <si>
     <t>输出2007年以后入社人的姓名</t>
-  </si>
-  <si>
-    <t>シート「SQL宿題_テーブルデータ」を参照する</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>作业10</t>
@@ -2733,6 +2692,518 @@
     </r>
     <phoneticPr fontId="22"/>
   </si>
+  <si>
+    <r>
+      <t>D:\soft\mysql-8.0.16-winx64\bin&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysqld --initialize --user=mysql --console</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D:\soft\mysql-8.0.16-winx64\bin&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysqld -install</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D:\soft\mysql-8.0.16-winx64\bin&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>net start mysql</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D:\soft\mysql-8.0.16-winx64\bin&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysql -u root -p</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">mysql&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>alter user root@localhost identified by '123456';</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">mysql&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>create database `mydb` character set utf8;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2019-07-06T12:30:55.638634Z 5 [Note] [MY-010454] [Server] A temporary password is generated for root@localhost: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>y4jsE?;-!fpj</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库的初期化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装数据库到系统服务里面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动MYSQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登陆MYSQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更改数据库的密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立数据库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从系统服务里面删除数据库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储过程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMP_NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定文字列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可变文字列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间戳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>。。。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YYYYMMDD。。。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLOB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLOB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理名（英文名）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑名（注释）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否是主键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可否为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是不是索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当作为检索条件时，会使检索速度加快。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T_EMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社员表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>番号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>性别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIRTHDAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SALARY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR(2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>number(6,2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非KEY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占用的是内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关系型的数据库系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORACLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲骨文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQLSERVER</t>
+  </si>
+  <si>
+    <t>SQLSERVER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微软</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DB2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYBASE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于银行证券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSTGRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQLITE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占用的是硬盘（表，视图，各种DDL）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQL语言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库操作工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysql workbench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQLの種類を分ける「DDL、DML、DCL」の紹介です。</t>
+  </si>
+  <si>
+    <t>🐡 DDL(Data Definition Language)</t>
+  </si>
+  <si>
+    <t>DDL(Data Definition Language)は、CREATEやDROP、ALTERなどデータベースオブジェクトの生成や削除変更を行うコマンドです。</t>
+  </si>
+  <si>
+    <t>🍄 DML(Data Manipulation Language)</t>
+  </si>
+  <si>
+    <r>
+      <t>DML(Data Manipulation Language)はSELECT/INSERT/UPDATE/DELETEなどテーブルに対するデータの取得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>追加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>削除を行うコマンドです。</t>
+    </r>
+  </si>
+  <si>
+    <t>🎂 DCL(Data Control Language)</t>
+  </si>
+  <si>
+    <t>DCL(Data Control Language)はBEGIN、COMMIT、ROLLBACKなどトランザクションの制御を行うためのコマンドです。</t>
+  </si>
+  <si>
+    <t>シート「SQL宿題1」を参照する
+根据行1-44之间的表结构，写出SQL建表语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2741,7 +3212,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;月&quot;dd&quot;日&quot;\(aaa\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2902,8 +3373,21 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2961,6 +3445,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3337,7 +3827,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -3471,6 +3961,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3516,9 +4009,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3890,13 +4393,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>494809</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>2790</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3934,13 +4437,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>542086</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>75833</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3978,13 +4481,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>146</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>342343</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>142113</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4022,14 +4525,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>191</xdr:row>
+      <xdr:row>180</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>466417</xdr:colOff>
-      <xdr:row>196</xdr:row>
-      <xdr:rowOff>85573</xdr:rowOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>85572</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4066,14 +4569,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>173</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>170743</xdr:colOff>
-      <xdr:row>189</xdr:row>
-      <xdr:rowOff>177295</xdr:rowOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4110,14 +4613,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>204</xdr:row>
+      <xdr:row>193</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>370486</xdr:colOff>
-      <xdr:row>215</xdr:row>
-      <xdr:rowOff>123482</xdr:rowOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>123483</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4154,13 +4657,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>186</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>399315</xdr:colOff>
-      <xdr:row>202</xdr:row>
+      <xdr:row>191</xdr:row>
       <xdr:rowOff>152249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4198,13 +4701,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>217</xdr:row>
+      <xdr:row>206</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123295</xdr:colOff>
-      <xdr:row>231</xdr:row>
+      <xdr:row>220</xdr:row>
       <xdr:rowOff>123393</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4242,13 +4745,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>232</xdr:row>
+      <xdr:row>221</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>237495</xdr:colOff>
-      <xdr:row>241</xdr:row>
+      <xdr:row>230</xdr:row>
       <xdr:rowOff>123542</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4280,6 +4783,196 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F587AC-B990-48F9-8774-B4EE11FD81D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8585200" y="13252450"/>
+          <a:ext cx="1181100" cy="184150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="コネクタ: カギ線 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9430CF94-1043-434C-AF4D-CEEA35C18F72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="5207000" y="10928350"/>
+          <a:ext cx="1460500" cy="6477000"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>615950</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C785DF9-BBA5-436D-B212-A7DD11BCA82A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1860550" y="26162000"/>
+          <a:ext cx="2057400" cy="158750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5851,7 +6544,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="49" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="2:4">
@@ -5863,7 +6556,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -5872,10 +6565,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:4">
@@ -5887,7 +6580,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -5899,7 +6592,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -5908,10 +6601,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="2:4">
@@ -5923,7 +6616,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -5935,7 +6628,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -5944,10 +6637,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -5959,7 +6652,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="2:4">
@@ -6014,6 +6707,789 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9A3152-A9D7-4010-9135-0CA38D711DB4}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="B2:J32"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="D7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="25" spans="4:10">
+      <c r="D25" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="32" spans="4:10">
+      <c r="J32" t="s">
+        <v>545</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF83579-325F-493D-9B2E-2B6CF3FFB5BE}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:E99"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.4140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.9140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16">
+      <c r="A2" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16">
+      <c r="A3" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16">
+      <c r="A4" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16">
+      <c r="A5" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16">
+      <c r="A11" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16">
+      <c r="A12" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16">
+      <c r="A13" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16">
+      <c r="A14" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16">
+      <c r="A27" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16">
+      <c r="A28" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16">
+      <c r="A29" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16">
+      <c r="A30" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16">
+      <c r="A38" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16">
+      <c r="A39" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16">
+      <c r="A40" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16">
+      <c r="A41" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="22" customFormat="1" ht="21"/>
+    <row r="47" spans="1:5" s="22" customFormat="1" ht="21">
+      <c r="B47" s="22" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="22" customFormat="1" ht="21"/>
+    <row r="49" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="50" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="51" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="52" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="53" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="54" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B54" s="22" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="56" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="57" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="58" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="59" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="60" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="61" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="62" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="63" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="64" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="65" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="66" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="67" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="68" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B68" s="22" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B69" s="22" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="71" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="72" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="73" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="74" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="75" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="76" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="77" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B77" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="79" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="80" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="81" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="82" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="83" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B83" s="22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="85" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="86" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="87" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="88" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="89" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="90" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="91" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="92" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="93" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B93" s="22" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="95" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="96" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="97" s="22" customFormat="1" ht="21"/>
+    <row r="98" s="22" customFormat="1" ht="21"/>
+    <row r="99" s="22" customFormat="1" ht="21"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CA0124-BB09-4A5F-B469-7554949501A3}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -6029,10 +7505,10 @@
         <v>136</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16">
@@ -6040,13 +7516,13 @@
         <v>139</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16">
@@ -6054,13 +7530,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16">
@@ -6068,7 +7544,7 @@
         <v>147</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>149</v>
@@ -6096,13 +7572,13 @@
         <v>154</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6110,13 +7586,13 @@
         <v>158</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6124,13 +7600,13 @@
         <v>162</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6138,13 +7614,13 @@
         <v>180</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6152,10 +7628,10 @@
         <v>136</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16">
@@ -6163,28 +7639,28 @@
         <v>139</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>199</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="J12" s="18" t="s">
         <v>360</v>
@@ -6195,28 +7671,28 @@
         <v>143</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="J13" s="18" t="s">
         <v>171</v>
@@ -6245,10 +7721,10 @@
         <v>205</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>173</v>
@@ -6291,28 +7767,28 @@
         <v>154</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>206</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>207</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="J16" s="16"/>
     </row>
@@ -6321,28 +7797,28 @@
         <v>158</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>207</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="J17" s="16"/>
     </row>
@@ -6351,28 +7827,28 @@
         <v>162</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>216</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>212</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="J18" s="16"/>
     </row>
@@ -6381,28 +7857,28 @@
         <v>180</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>206</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>207</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="J19" s="16"/>
     </row>
@@ -6411,122 +7887,122 @@
         <v>182</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>214</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>212</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="J20" s="16"/>
     </row>
     <row r="24" spans="1:10">
       <c r="B24" s="27" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="15" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="15" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="15" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="15" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="15" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="15" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="15" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="15" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="B34" s="27" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="15" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="15" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -6538,7 +8014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A7714B-D9DD-416F-B392-2E2CEF359F1C}">
   <sheetPr>
     <tabColor theme="7"/>
@@ -6553,7 +8029,7 @@
   <sheetData>
     <row r="2" spans="3:26">
       <c r="F2" s="52" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="3:26">
@@ -6578,19 +8054,19 @@
     </row>
     <row r="5" spans="3:26">
       <c r="U5" s="75" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="V5" s="75" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="W5" s="75" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="X5" s="75" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="Y5" s="75" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="14.5" thickBot="1"/>
@@ -6625,7 +8101,7 @@
       <c r="D8" s="57"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="57"/>
@@ -6639,14 +8115,14 @@
       <c r="P8" s="57"/>
       <c r="Q8" s="57"/>
       <c r="R8" s="57" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="S8" s="57"/>
       <c r="T8" s="57"/>
       <c r="U8" s="78"/>
       <c r="V8" s="78"/>
       <c r="W8" s="78" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="X8" s="78"/>
       <c r="Y8" s="78"/>
@@ -6657,7 +8133,7 @@
       <c r="D9" s="57"/>
       <c r="E9" s="58"/>
       <c r="F9" s="62" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="G9" s="63"/>
       <c r="H9" s="63"/>
@@ -6712,16 +8188,16 @@
       <c r="E11" s="58"/>
       <c r="F11" s="65"/>
       <c r="G11" s="68" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="H11" s="68" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="I11" s="68" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="J11" s="68" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="K11" s="63"/>
       <c r="L11" s="63"/>
@@ -6773,10 +8249,10 @@
       <c r="G13" s="69"/>
       <c r="H13" s="69"/>
       <c r="I13" s="69" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="K13" s="66"/>
       <c r="L13" s="66"/>
@@ -6803,7 +8279,7 @@
       <c r="G14" s="69"/>
       <c r="H14" s="69"/>
       <c r="I14" s="69" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="J14" s="69"/>
       <c r="K14" s="66"/>
@@ -6852,7 +8328,7 @@
     <row r="16" spans="3:26" ht="14.5" thickBot="1">
       <c r="C16" s="56"/>
       <c r="D16" s="57" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="E16" s="58"/>
       <c r="F16" s="65"/>
@@ -6908,13 +8384,13 @@
       <c r="D18" s="57"/>
       <c r="E18" s="58"/>
       <c r="F18" s="56" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="G18" s="57"/>
       <c r="H18" s="57"/>
       <c r="I18" s="57"/>
       <c r="J18" s="53" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="K18" s="54"/>
       <c r="L18" s="54"/>
@@ -6938,14 +8414,14 @@
       <c r="D19" s="57"/>
       <c r="E19" s="58"/>
       <c r="F19" s="56" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="G19" s="57"/>
       <c r="H19" s="57"/>
       <c r="I19" s="57"/>
       <c r="J19" s="56"/>
       <c r="K19" s="57" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="L19" s="57"/>
       <c r="M19" s="57"/>
@@ -6968,7 +8444,7 @@
       <c r="D20" s="57"/>
       <c r="E20" s="58"/>
       <c r="F20" s="56" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="G20" s="57"/>
       <c r="H20" s="57"/>
@@ -6996,7 +8472,7 @@
       <c r="D21" s="57"/>
       <c r="E21" s="58"/>
       <c r="F21" s="56" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="G21" s="57"/>
       <c r="H21" s="57"/>
@@ -7024,7 +8500,7 @@
       <c r="D22" s="57"/>
       <c r="E22" s="58"/>
       <c r="F22" s="56" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="G22" s="57"/>
       <c r="H22" s="57"/>
@@ -7052,7 +8528,7 @@
       <c r="D23" s="57"/>
       <c r="E23" s="58"/>
       <c r="F23" s="56" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="G23" s="57"/>
       <c r="H23" s="57"/>
@@ -7080,7 +8556,7 @@
       <c r="D24" s="57"/>
       <c r="E24" s="58"/>
       <c r="F24" s="56" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="G24" s="57"/>
       <c r="H24" s="57"/>
@@ -7108,7 +8584,7 @@
       <c r="D25" s="57"/>
       <c r="E25" s="58"/>
       <c r="F25" s="56" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="G25" s="57"/>
       <c r="H25" s="57"/>
@@ -7136,7 +8612,7 @@
       <c r="D26" s="57"/>
       <c r="E26" s="58"/>
       <c r="F26" s="59" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="G26" s="60"/>
       <c r="H26" s="60"/>
@@ -7192,7 +8668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41AFFA43-4820-4AD6-9E6A-7F8B8CFA34B7}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -7202,7 +8678,7 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="42" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -7215,7 +8691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF30867F-4987-428B-B1BA-79BEE1AC7E24}">
   <dimension ref="B1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7286,7 +8762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D3055-B4C0-44F8-BC38-3332800489E4}">
   <dimension ref="B1:S32"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7461,7 +8937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBA7452-ADCF-4916-B20B-0512AE3ED3F2}">
   <dimension ref="B1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7530,7 +9006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A228C4-8BB0-42F2-86E2-63F3E8493370}">
   <dimension ref="B1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7591,7 +9067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C125254-9191-4F9A-8C38-B14BF103FA27}">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7643,151 +9119,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E4EC444-DA0C-43AC-8DA7-D83AAF18CFD5}">
-  <dimension ref="B1:S26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="2.5" style="20" customWidth="1"/>
-    <col min="2" max="16384" width="8.6640625" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:19" ht="16">
-      <c r="B1" s="23" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="2" spans="2:19" ht="16">
-      <c r="B2" s="23"/>
-    </row>
-    <row r="3" spans="2:19">
-      <c r="R3" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19">
-      <c r="R4" s="20" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19">
-      <c r="R5" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19">
-      <c r="R6" s="20" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19">
-      <c r="R7" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19">
-      <c r="R8" s="20" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19">
-      <c r="R9" s="20" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19">
-      <c r="R10" s="20" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19">
-      <c r="R11" s="20" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19">
-      <c r="R12" s="20" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19">
-      <c r="R13" s="20" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19">
-      <c r="R14" s="20" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19">
-      <c r="R15" s="20" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19">
-      <c r="S16" s="20" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="17" spans="18:18">
-      <c r="R17" s="20" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="18" spans="18:18">
-      <c r="R18" s="20" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="19" spans="18:18">
-      <c r="R19" s="20" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="20" spans="18:18">
-      <c r="R20" s="20" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="21" spans="18:18">
-      <c r="R21" s="20" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="22" spans="18:18">
-      <c r="R22" s="20" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="23" spans="18:18">
-      <c r="R23" s="20" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="24" spans="18:18">
-      <c r="R24" s="20" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="25" spans="18:18">
-      <c r="R25" s="20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="18:18">
-      <c r="R26" s="20" t="s">
-        <v>359</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7801,67 +9132,67 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="43" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="42" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="43" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" s="41" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="41" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="41" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="42" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="41" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -7871,6 +9202,151 @@
     <hyperlink ref="B3" r:id="rId2" xr:uid="{FDF9A291-A36E-435B-8248-0C8EED933B36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E4EC444-DA0C-43AC-8DA7-D83AAF18CFD5}">
+  <dimension ref="B1:S26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.5" style="20" customWidth="1"/>
+    <col min="2" max="16384" width="8.6640625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="16">
+      <c r="B1" s="23" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="2:19" ht="16">
+      <c r="B2" s="23"/>
+    </row>
+    <row r="3" spans="2:19">
+      <c r="R3" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="R4" s="20" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19">
+      <c r="R5" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="R6" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="R7" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="R8" s="20" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="R9" s="20" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="R10" s="20" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19">
+      <c r="R11" s="20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="R12" s="20" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="R13" s="20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19">
+      <c r="R14" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
+      <c r="R15" s="20" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="S16" s="20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17" spans="18:18">
+      <c r="R17" s="20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="18:18">
+      <c r="R18" s="20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19" spans="18:18">
+      <c r="R19" s="20" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="20" spans="18:18">
+      <c r="R20" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" spans="18:18">
+      <c r="R21" s="20" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="18:18">
+      <c r="R22" s="20" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="18:18">
+      <c r="R23" s="20" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="18:18">
+      <c r="R24" s="20" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="25" spans="18:18">
+      <c r="R25" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="18:18">
+      <c r="R26" s="20" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7905,7 +9381,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>5</v>
@@ -7915,7 +9391,7 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="88" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6">
@@ -7934,7 +9410,7 @@
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="89" t="s">
+      <c r="H3" s="92" t="s">
         <v>14</v>
       </c>
       <c r="J3" s="33">
@@ -7942,7 +9418,7 @@
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="86"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="6">
         <f>$J$3</f>
         <v>44598</v>
@@ -7959,10 +9435,10 @@
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="90"/>
+      <c r="H4" s="93"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="86"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="6">
         <f>$J$3</f>
         <v>44598</v>
@@ -7979,10 +9455,10 @@
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="90"/>
+      <c r="H5" s="93"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="86"/>
+      <c r="B6" s="89"/>
       <c r="C6" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -7999,12 +9475,12 @@
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="89" t="s">
+      <c r="H6" s="92" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="86"/>
+      <c r="B7" s="89"/>
       <c r="C7" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -8021,10 +9497,10 @@
       <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="90"/>
+      <c r="H7" s="93"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="86"/>
+      <c r="B8" s="89"/>
       <c r="C8" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -8041,10 +9517,10 @@
       <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="90"/>
+      <c r="H8" s="93"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="86"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -8061,12 +9537,12 @@
       <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="90" t="s">
+      <c r="H9" s="93" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="86"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -8083,10 +9559,10 @@
       <c r="G10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="90"/>
+      <c r="H10" s="93"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="86"/>
+      <c r="B11" s="89"/>
       <c r="C11" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -8103,10 +9579,10 @@
       <c r="G11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="90"/>
+      <c r="H11" s="93"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="86"/>
+      <c r="B12" s="89"/>
       <c r="C12" s="6">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -8123,12 +9599,12 @@
       <c r="G12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="89" t="s">
-        <v>512</v>
+      <c r="H12" s="92" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="86"/>
+      <c r="B13" s="89"/>
       <c r="C13" s="6">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -8145,10 +9621,10 @@
       <c r="G13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="90"/>
+      <c r="H13" s="93"/>
     </row>
     <row r="14" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B14" s="87"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="28">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -8165,10 +9641,10 @@
       <c r="G14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="91"/>
+      <c r="H14" s="94"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="88" t="s">
+      <c r="B15" s="91" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="29">
@@ -8185,9 +9661,9 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="H15" s="92" t="s">
+        <v>508</v>
+      </c>
+      <c r="H15" s="95" t="s">
         <v>42</v>
       </c>
       <c r="J15" s="33">
@@ -8195,7 +9671,7 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="86"/>
+      <c r="B16" s="89"/>
       <c r="C16" s="6">
         <f>$J$15</f>
         <v>44626</v>
@@ -8210,12 +9686,12 @@
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="H16" s="90"/>
+        <v>507</v>
+      </c>
+      <c r="H16" s="93"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="86"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="6">
         <f>$J$15</f>
         <v>44626</v>
@@ -8230,12 +9706,12 @@
         <v>3</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="H17" s="90"/>
+        <v>384</v>
+      </c>
+      <c r="H17" s="93"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="86"/>
+      <c r="B18" s="89"/>
       <c r="C18" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -8252,12 +9728,12 @@
       <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="93" t="s">
+      <c r="H18" s="96" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="86"/>
+      <c r="B19" s="89"/>
       <c r="C19" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -8274,10 +9750,10 @@
       <c r="G19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="90"/>
+      <c r="H19" s="93"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="86"/>
+      <c r="B20" s="89"/>
       <c r="C20" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -8294,10 +9770,10 @@
       <c r="G20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="90"/>
+      <c r="H20" s="93"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="86"/>
+      <c r="B21" s="89"/>
       <c r="C21" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -8314,12 +9790,12 @@
       <c r="G21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="90" t="s">
-        <v>398</v>
+      <c r="H21" s="93" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="86"/>
+      <c r="B22" s="89"/>
       <c r="C22" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -8336,10 +9812,10 @@
       <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="90"/>
+      <c r="H22" s="93"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="86"/>
+      <c r="B23" s="89"/>
       <c r="C23" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -8356,10 +9832,10 @@
       <c r="G23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="90"/>
+      <c r="H23" s="93"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="86"/>
+      <c r="B24" s="89"/>
       <c r="C24" s="6">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -8376,12 +9852,12 @@
       <c r="G24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="90" t="s">
-        <v>394</v>
+      <c r="H24" s="93" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="86"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="6">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -8398,10 +9874,10 @@
       <c r="G25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="90"/>
+      <c r="H25" s="93"/>
     </row>
     <row r="26" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B26" s="87"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="30">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -8418,10 +9894,10 @@
       <c r="G26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="94"/>
+      <c r="H26" s="97"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="91" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="31">
@@ -8440,15 +9916,15 @@
       <c r="G27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="95" t="s">
-        <v>480</v>
+      <c r="H27" s="111" t="s">
+        <v>643</v>
       </c>
       <c r="J27" s="33">
         <v>44654</v>
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="86"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="6">
         <f>$J$27</f>
         <v>44654</v>
@@ -8465,10 +9941,10 @@
       <c r="G28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="90"/>
+      <c r="H28" s="93"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="86"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="6">
         <f>$J$27</f>
         <v>44654</v>
@@ -8485,10 +9961,10 @@
       <c r="G29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="90"/>
+      <c r="H29" s="93"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="86"/>
+      <c r="B30" s="89"/>
       <c r="C30" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -8505,12 +9981,12 @@
       <c r="G30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="90" t="s">
-        <v>524</v>
+      <c r="H30" s="93" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="86"/>
+      <c r="B31" s="89"/>
       <c r="C31" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -8527,10 +10003,10 @@
       <c r="G31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H31" s="90"/>
+      <c r="H31" s="93"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="86"/>
+      <c r="B32" s="89"/>
       <c r="C32" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -8547,10 +10023,10 @@
       <c r="G32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H32" s="90"/>
+      <c r="H32" s="93"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="86"/>
+      <c r="B33" s="89"/>
       <c r="C33" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -8567,12 +10043,12 @@
       <c r="G33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="89" t="s">
-        <v>525</v>
+      <c r="H33" s="92" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="86"/>
+      <c r="B34" s="89"/>
       <c r="C34" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -8589,10 +10065,10 @@
       <c r="G34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H34" s="90"/>
+      <c r="H34" s="93"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="86"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -8609,10 +10085,10 @@
       <c r="G35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H35" s="90"/>
+      <c r="H35" s="93"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="86"/>
+      <c r="B36" s="89"/>
       <c r="C36" s="6">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -8627,14 +10103,14 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="H36" s="89" t="s">
-        <v>526</v>
+        <v>470</v>
+      </c>
+      <c r="H36" s="92" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="86"/>
+      <c r="B37" s="89"/>
       <c r="C37" s="6">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -8651,10 +10127,10 @@
       <c r="G37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="90"/>
+      <c r="H37" s="93"/>
     </row>
     <row r="38" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B38" s="87"/>
+      <c r="B38" s="90"/>
       <c r="C38" s="28">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -8671,7 +10147,7 @@
       <c r="G38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="91"/>
+      <c r="H38" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -8732,7 +10208,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>4</v>
@@ -8742,8 +10218,8 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="85" t="s">
-        <v>490</v>
+      <c r="B3" s="88" t="s">
+        <v>476</v>
       </c>
       <c r="C3" s="6">
         <f>$J$3</f>
@@ -8761,15 +10237,15 @@
       <c r="G3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="89" t="s">
-        <v>517</v>
+      <c r="H3" s="92" t="s">
+        <v>503</v>
       </c>
       <c r="J3" s="33">
         <v>44689</v>
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="96"/>
+      <c r="B4" s="99"/>
       <c r="C4" s="6">
         <f>$J$3</f>
         <v>44689</v>
@@ -8786,10 +10262,10 @@
       <c r="G4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="90"/>
+      <c r="H4" s="93"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="96"/>
+      <c r="B5" s="99"/>
       <c r="C5" s="6">
         <f>$J$3</f>
         <v>44689</v>
@@ -8806,10 +10282,10 @@
       <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="90"/>
+      <c r="H5" s="93"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="96"/>
+      <c r="B6" s="99"/>
       <c r="C6" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -8824,14 +10300,14 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="H6" s="89" t="s">
-        <v>485</v>
+        <v>473</v>
+      </c>
+      <c r="H6" s="92" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="96"/>
+      <c r="B7" s="99"/>
       <c r="C7" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -8846,12 +10322,12 @@
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="H7" s="90"/>
+        <v>473</v>
+      </c>
+      <c r="H7" s="93"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="96"/>
+      <c r="B8" s="99"/>
       <c r="C8" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -8866,12 +10342,12 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="H8" s="90"/>
+        <v>473</v>
+      </c>
+      <c r="H8" s="93"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="96"/>
+      <c r="B9" s="99"/>
       <c r="C9" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -8886,12 +10362,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="H9" s="90"/>
+        <v>472</v>
+      </c>
+      <c r="H9" s="93"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="96"/>
+      <c r="B10" s="99"/>
       <c r="C10" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -8906,12 +10382,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="H10" s="90"/>
+        <v>472</v>
+      </c>
+      <c r="H10" s="93"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="96"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -8928,10 +10404,10 @@
       <c r="G11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="90"/>
+      <c r="H11" s="93"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="96"/>
+      <c r="B12" s="99"/>
       <c r="C12" s="6">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -8948,10 +10424,10 @@
       <c r="G12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="90"/>
+      <c r="H12" s="93"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="96"/>
+      <c r="B13" s="99"/>
       <c r="C13" s="6">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -8968,10 +10444,10 @@
       <c r="G13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="90"/>
+      <c r="H13" s="93"/>
     </row>
     <row r="14" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B14" s="96"/>
+      <c r="B14" s="99"/>
       <c r="C14" s="28">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -8988,10 +10464,10 @@
       <c r="G14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="91"/>
+      <c r="H14" s="94"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="96"/>
+      <c r="B15" s="99"/>
       <c r="C15" s="29">
         <f>$J$15</f>
         <v>44717</v>
@@ -9008,13 +10484,13 @@
       <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="99"/>
+      <c r="H15" s="102"/>
       <c r="J15" s="33">
         <v>44717</v>
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="96"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="6">
         <f>$J$15</f>
         <v>44717</v>
@@ -9031,10 +10507,10 @@
       <c r="G16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="90"/>
+      <c r="H16" s="93"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="96"/>
+      <c r="B17" s="99"/>
       <c r="C17" s="6">
         <f>$J$15</f>
         <v>44717</v>
@@ -9051,10 +10527,10 @@
       <c r="G17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="90"/>
+      <c r="H17" s="93"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="96"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -9071,10 +10547,10 @@
       <c r="G18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="90"/>
+      <c r="H18" s="93"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="96"/>
+      <c r="B19" s="99"/>
       <c r="C19" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -9091,10 +10567,10 @@
       <c r="G19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="90"/>
+      <c r="H19" s="93"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="96"/>
+      <c r="B20" s="99"/>
       <c r="C20" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -9111,10 +10587,10 @@
       <c r="G20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="90"/>
+      <c r="H20" s="93"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="96"/>
+      <c r="B21" s="99"/>
       <c r="C21" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -9131,10 +10607,10 @@
       <c r="G21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="90"/>
+      <c r="H21" s="93"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="96"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -9151,10 +10627,10 @@
       <c r="G22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="90"/>
+      <c r="H22" s="93"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="96"/>
+      <c r="B23" s="99"/>
       <c r="C23" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -9171,10 +10647,10 @@
       <c r="G23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="90"/>
+      <c r="H23" s="93"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="96"/>
+      <c r="B24" s="99"/>
       <c r="C24" s="6">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -9191,10 +10667,10 @@
       <c r="G24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="90"/>
+      <c r="H24" s="93"/>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="96"/>
+      <c r="B25" s="99"/>
       <c r="C25" s="6">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -9211,10 +10687,10 @@
       <c r="G25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="90"/>
+      <c r="H25" s="93"/>
     </row>
     <row r="26" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B26" s="97"/>
+      <c r="B26" s="100"/>
       <c r="C26" s="30">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -9231,11 +10707,11 @@
       <c r="G26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="94"/>
+      <c r="H26" s="97"/>
     </row>
     <row r="27" spans="2:10" ht="14" customHeight="1">
-      <c r="B27" s="98" t="s">
-        <v>489</v>
+      <c r="B27" s="101" t="s">
+        <v>475</v>
       </c>
       <c r="C27" s="31">
         <f>$J$27</f>
@@ -9253,15 +10729,15 @@
       <c r="G27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="95" t="s">
-        <v>518</v>
+      <c r="H27" s="98" t="s">
+        <v>504</v>
       </c>
       <c r="J27" s="33">
         <v>44745</v>
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="96"/>
+      <c r="B28" s="99"/>
       <c r="C28" s="6">
         <f>$J$27</f>
         <v>44745</v>
@@ -9278,10 +10754,10 @@
       <c r="G28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="90"/>
+      <c r="H28" s="93"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="96"/>
+      <c r="B29" s="99"/>
       <c r="C29" s="6">
         <f>$J$27</f>
         <v>44745</v>
@@ -9298,10 +10774,10 @@
       <c r="G29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="90"/>
+      <c r="H29" s="93"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="96"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -9316,14 +10792,14 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H30" s="90" t="s">
-        <v>520</v>
+        <v>505</v>
+      </c>
+      <c r="H30" s="93" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="96"/>
+      <c r="B31" s="99"/>
       <c r="C31" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -9338,12 +10814,12 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H31" s="90"/>
+        <v>505</v>
+      </c>
+      <c r="H31" s="93"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="96"/>
+      <c r="B32" s="99"/>
       <c r="C32" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -9358,13 +10834,13 @@
         <v>3</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H32" s="90"/>
+        <v>505</v>
+      </c>
+      <c r="H32" s="93"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="96" t="s">
-        <v>527</v>
+      <c r="B33" s="99" t="s">
+        <v>513</v>
       </c>
       <c r="C33" s="6">
         <f>$J$27+14</f>
@@ -9382,10 +10858,10 @@
       <c r="G33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="90"/>
+      <c r="H33" s="93"/>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="96"/>
+      <c r="B34" s="99"/>
       <c r="C34" s="6">
         <f>$J$27+14</f>
         <v>44759</v>
@@ -9402,10 +10878,10 @@
       <c r="G34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="90"/>
+      <c r="H34" s="93"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="96"/>
+      <c r="B35" s="99"/>
       <c r="C35" s="6">
         <f>$J$27+14</f>
         <v>44759</v>
@@ -9422,11 +10898,11 @@
       <c r="G35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H35" s="90"/>
+      <c r="H35" s="93"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="96" t="s">
-        <v>528</v>
+      <c r="B36" s="99" t="s">
+        <v>514</v>
       </c>
       <c r="C36" s="6">
         <f>$J$27+21</f>
@@ -9442,12 +10918,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="H36" s="90"/>
+        <v>502</v>
+      </c>
+      <c r="H36" s="93"/>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="86"/>
+      <c r="B37" s="89"/>
       <c r="C37" s="6">
         <f>$J$27+21</f>
         <v>44766</v>
@@ -9462,12 +10938,12 @@
         <v>2</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H37" s="90"/>
+        <v>501</v>
+      </c>
+      <c r="H37" s="93"/>
     </row>
     <row r="38" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B38" s="87"/>
+      <c r="B38" s="90"/>
       <c r="C38" s="28">
         <f>$J$27+21</f>
         <v>44766</v>
@@ -9482,12 +10958,18 @@
         <v>3</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="H38" s="91"/>
+        <v>501</v>
+      </c>
+      <c r="H38" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="H33:H35"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="B33:B35"/>
     <mergeCell ref="B3:B26"/>
     <mergeCell ref="B27:B32"/>
     <mergeCell ref="H3:H5"/>
@@ -9498,12 +10980,6 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="H24:H26"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="H33:H35"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="B33:B35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9519,212 +10995,171 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A70:B246"/>
+  <dimension ref="A70:U107"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="70" spans="2:2" ht="15.5">
+    <row r="70" spans="2:21" ht="15.5">
       <c r="B70" s="11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="72" spans="2:2" ht="15.5">
+    <row r="72" spans="2:21" ht="15.5">
       <c r="B72" s="11" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="73" spans="2:2" ht="15.5">
+    <row r="73" spans="2:21" ht="15.5">
       <c r="B73" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="U73" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" ht="15.5">
+      <c r="B74" s="11" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="74" spans="2:2" ht="15.5">
-      <c r="B74" s="11" t="s">
+    <row r="75" spans="2:21" ht="15.5">
+      <c r="B75" s="11" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" ht="15.5">
+      <c r="B76" s="11" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="75" spans="2:2" ht="15.5">
-      <c r="B75" s="11" t="s">
+    <row r="77" spans="2:21" ht="15.5">
+      <c r="B77" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="U77" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="78" spans="2:21" ht="15.5">
+      <c r="B78" s="11" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="76" spans="2:2" ht="15.5">
-      <c r="B76" s="11" t="s">
+    <row r="79" spans="2:21" ht="15.5">
+      <c r="B79" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="U79" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="80" spans="2:21" ht="15.5">
+      <c r="B80" s="11" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="77" spans="2:2" ht="15.5">
-      <c r="B77" s="11" t="s">
+    <row r="81" spans="2:21" ht="15.5">
+      <c r="B81" s="11" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="78" spans="2:2" ht="15.5">
-      <c r="B78" s="11" t="s">
+    <row r="82" spans="2:21" ht="15.5">
+      <c r="B82" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="U82" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="83" spans="2:21" ht="15.5">
+      <c r="B83" s="11" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" ht="15.5">
-      <c r="B79" s="11" t="s">
+      <c r="U83" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" spans="2:21" ht="15.5">
+      <c r="B84" s="11" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="80" spans="2:2" ht="15.5">
-      <c r="B80" s="11" t="s">
+    <row r="85" spans="2:21" ht="15.5">
+      <c r="B85" s="11" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="81" spans="2:2" ht="15.5">
-      <c r="B81" s="11" t="s">
+    <row r="86" spans="2:21" ht="15.5">
+      <c r="B86" s="11" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="82" spans="2:2" ht="15.5">
-      <c r="B82" s="11" t="s">
+    <row r="87" spans="2:21" ht="15.5">
+      <c r="B87" s="11" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="83" spans="2:2" ht="15.5">
-      <c r="B83" s="11" t="s">
+    <row r="88" spans="2:21" ht="15.5">
+      <c r="B88" s="11" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="15.5">
-      <c r="B84" s="11" t="s">
+    <row r="89" spans="2:21" ht="15.5">
+      <c r="B89" s="11" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="15.5">
-      <c r="B85" s="11" t="s">
+    <row r="90" spans="2:21" ht="15.5">
+      <c r="B90" s="11" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="86" spans="2:2" ht="15.5">
-      <c r="B86" s="11" t="s">
+    <row r="91" spans="2:21" ht="15.5">
+      <c r="B91" s="11" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="87" spans="2:2" ht="15.5">
-      <c r="B87" s="11" t="s">
+    <row r="92" spans="2:21" ht="15.5">
+      <c r="B92" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="U92" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="93" spans="2:21" ht="15.5">
+      <c r="B93" s="11" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="88" spans="2:2" ht="15.5">
-      <c r="B88" s="11" t="s">
+    <row r="94" spans="2:21" ht="15.5">
+      <c r="B94" s="11" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="95" spans="2:21" ht="15.5">
+      <c r="B95" s="11" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" ht="15.5">
-      <c r="B89" s="11" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" ht="15.5">
-      <c r="B90" s="11" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" ht="15.5">
-      <c r="B91" s="11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" ht="15.5">
-      <c r="B92" s="11" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" ht="15.5">
-      <c r="B93" s="11" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" ht="15.5">
-      <c r="B94" s="11" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="15.5">
-      <c r="B95" s="11" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" ht="15.5">
-      <c r="B96" s="11" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" ht="15.5">
-      <c r="B97" s="11" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" ht="15.5">
-      <c r="B98" s="11" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" ht="15.5">
-      <c r="B99" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" ht="15.5">
-      <c r="B100" s="11" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" ht="15.5">
-      <c r="B101" s="11" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" ht="15.5">
-      <c r="B102" s="11" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" ht="15.5">
-      <c r="B103" s="11" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" ht="15.5">
-      <c r="B104" s="11" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" ht="15.5">
-      <c r="B105" s="11" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" ht="15.5">
-      <c r="B106" s="11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" ht="15.5">
-      <c r="B107" s="11" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" ht="15.5">
-      <c r="B108" s="11" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" s="100" customFormat="1">
-      <c r="A118" s="101" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" s="100" customFormat="1">
-      <c r="A244" s="100" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2">
-      <c r="B246" s="102" t="s">
+      <c r="U95" t="s">
         <v>563</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" s="85" customFormat="1">
+      <c r="A100" s="85" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="B102" s="87" t="s">
+        <v>549</v>
+      </c>
+      <c r="D102" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" s="85" customFormat="1">
+      <c r="A107" s="86" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -9736,6 +11171,522 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4778365C-B644-4608-92AF-A3C1AC394E78}">
+  <dimension ref="B2:K39"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6">
+      <c r="B2" s="43" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="C3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="D6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="C7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D7" s="105" t="s">
+        <v>616</v>
+      </c>
+      <c r="E7" s="105" t="s">
+        <v>617</v>
+      </c>
+      <c r="F7" s="105"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="D8" s="105" t="s">
+        <v>619</v>
+      </c>
+      <c r="E8" s="105" t="s">
+        <v>620</v>
+      </c>
+      <c r="F8" s="105"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="D9" s="105" t="s">
+        <v>621</v>
+      </c>
+      <c r="E9" s="105" t="s">
+        <v>622</v>
+      </c>
+      <c r="F9" s="105"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="D10" s="105" t="s">
+        <v>623</v>
+      </c>
+      <c r="E10" s="105" t="s">
+        <v>624</v>
+      </c>
+      <c r="F10" s="105"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="C11" t="s">
+        <v>628</v>
+      </c>
+      <c r="D11" s="108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="D12" s="108" t="s">
+        <v>625</v>
+      </c>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="D13" s="108" t="s">
+        <v>626</v>
+      </c>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="43" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="C16" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="43" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="C21" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="C23" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="C24" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="C26" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="C27" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="C29" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="C30" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="D35" s="109" t="s">
+        <v>616</v>
+      </c>
+      <c r="E35" s="109" t="s">
+        <v>619</v>
+      </c>
+      <c r="F35" s="109" t="s">
+        <v>621</v>
+      </c>
+      <c r="G35" s="109" t="s">
+        <v>623</v>
+      </c>
+      <c r="H35" s="109" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="109" t="s">
+        <v>625</v>
+      </c>
+      <c r="J35" s="109" t="s">
+        <v>626</v>
+      </c>
+      <c r="K35" s="109"/>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="C36" t="s">
+        <v>632</v>
+      </c>
+      <c r="D36" s="110" t="s">
+        <v>633</v>
+      </c>
+      <c r="E36" s="110" t="s">
+        <v>633</v>
+      </c>
+      <c r="F36" s="110" t="s">
+        <v>633</v>
+      </c>
+      <c r="G36" s="110" t="s">
+        <v>633</v>
+      </c>
+      <c r="H36" s="110" t="s">
+        <v>633</v>
+      </c>
+      <c r="I36" s="110" t="s">
+        <v>633</v>
+      </c>
+      <c r="J36" s="110" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="C37" t="s">
+        <v>634</v>
+      </c>
+      <c r="H37" s="110" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="C38" t="s">
+        <v>635</v>
+      </c>
+      <c r="I38" s="110" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="C39" t="s">
+        <v>618</v>
+      </c>
+      <c r="E39" s="110" t="s">
+        <v>633</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394CD3A8-85DA-4DD6-84BA-17B06DB50AEB}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B2:H41"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="3" max="3" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.58203125" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="D3" s="104" t="s">
+        <v>593</v>
+      </c>
+      <c r="E3" s="104" t="s">
+        <v>594</v>
+      </c>
+      <c r="F3" s="104" t="s">
+        <v>595</v>
+      </c>
+      <c r="G3" s="104" t="s">
+        <v>597</v>
+      </c>
+      <c r="H3" s="104" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="D4" s="104" t="s">
+        <v>569</v>
+      </c>
+      <c r="E4" s="104" t="s">
+        <v>599</v>
+      </c>
+      <c r="F4" s="104" t="s">
+        <v>600</v>
+      </c>
+      <c r="G4" s="104" t="s">
+        <v>598</v>
+      </c>
+      <c r="H4" s="104" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="D5" s="106" t="s">
+        <v>602</v>
+      </c>
+      <c r="E5" s="106" t="s">
+        <v>603</v>
+      </c>
+      <c r="F5" s="106" t="s">
+        <v>604</v>
+      </c>
+      <c r="G5" s="106" t="s">
+        <v>605</v>
+      </c>
+      <c r="H5" s="106" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="D6" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="D7" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="D8" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="C14" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="C15" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" s="105" t="s">
+        <v>582</v>
+      </c>
+      <c r="D17" s="105"/>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="C18" s="105"/>
+      <c r="D18" s="105" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="C19" s="105"/>
+      <c r="D19" s="105" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5">
+      <c r="C21" s="107" t="s">
+        <v>583</v>
+      </c>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+    </row>
+    <row r="22" spans="3:5">
+      <c r="C22" s="107"/>
+      <c r="D22" s="107" t="s">
+        <v>570</v>
+      </c>
+      <c r="E22" s="107"/>
+    </row>
+    <row r="23" spans="3:5">
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5">
+      <c r="C25" s="107"/>
+      <c r="D25" s="107" t="s">
+        <v>571</v>
+      </c>
+      <c r="E25" s="107"/>
+    </row>
+    <row r="26" spans="3:5">
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5">
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5">
+      <c r="C28" s="107"/>
+      <c r="D28" s="107" t="s">
+        <v>572</v>
+      </c>
+      <c r="E28" s="107" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5">
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5">
+      <c r="C31" s="107"/>
+      <c r="D31" s="107" t="s">
+        <v>580</v>
+      </c>
+      <c r="E31" s="107"/>
+    </row>
+    <row r="32" spans="3:5">
+      <c r="C32" s="107"/>
+      <c r="D32" s="107" t="s">
+        <v>581</v>
+      </c>
+      <c r="E32" s="107"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="C33" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="C34" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="C35" t="s">
+        <v>589</v>
+      </c>
+      <c r="H35" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" t="s">
+        <v>568</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2770712A-2474-4DDC-846E-D27829C2C72B}">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
@@ -10095,7 +12046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5493687F-4738-4AF1-A69E-E960970AE6FB}">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
@@ -11221,7 +13172,7 @@
     </row>
     <row r="243" spans="2:2" ht="16">
       <c r="B243" s="13" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="2:2">
@@ -11271,787 +13222,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9A3152-A9D7-4010-9135-0CA38D711DB4}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="B2:J32"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="C4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="D7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="25" spans="4:10">
-      <c r="D25" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="32" spans="4:10">
-      <c r="J32" t="s">
-        <v>559</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF83579-325F-493D-9B2E-2B6CF3FFB5BE}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="13.4140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.9140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16">
-      <c r="A2" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16">
-      <c r="A3" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16">
-      <c r="A4" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16">
-      <c r="A5" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16">
-      <c r="A11" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16">
-      <c r="A12" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16">
-      <c r="A13" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16">
-      <c r="A14" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="16">
-      <c r="A27" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="16">
-      <c r="A28" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="16">
-      <c r="A29" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="16">
-      <c r="A30" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="16">
-      <c r="A38" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="16">
-      <c r="A39" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="16">
-      <c r="A40" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="16">
-      <c r="A41" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="22" customFormat="1" ht="21"/>
-    <row r="47" spans="1:5" s="22" customFormat="1" ht="21">
-      <c r="B47" s="22" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="22" customFormat="1" ht="21"/>
-    <row r="49" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="50" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="51" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="52" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="53" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="54" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B54" s="22" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="56" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="57" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="58" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="59" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="60" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="61" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="62" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="63" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="64" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="65" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="66" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="67" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="68" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B68" s="22" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B69" s="22" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="71" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="72" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="73" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="74" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="75" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="76" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="77" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B77" s="22" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="79" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="80" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="81" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="82" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="83" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B83" s="22" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="85" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="86" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="87" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="88" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="89" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="90" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="91" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="92" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="93" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B93" s="22" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="95" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="96" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="97" s="22" customFormat="1" ht="21"/>
-    <row r="98" s="22" customFormat="1" ht="21"/>
-    <row r="99" s="22" customFormat="1" ht="21"/>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/IT授業内容(智源).xlsx
+++ b/IT授業内容(智源).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tech\git20220205\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142CFB3D-3777-4F7D-9E01-310CB312F92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E83844-1333-4411-940F-C46BB6A3E89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" tabRatio="809" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必要ツール" sheetId="3" r:id="rId1"/>
@@ -24,15 +24,16 @@
     <sheet name="SQLメモ" sheetId="5" r:id="rId9"/>
     <sheet name="JAVA宿題" sheetId="4" r:id="rId10"/>
     <sheet name="SQL宿題1" sheetId="6" r:id="rId11"/>
-    <sheet name="SQL宿題2" sheetId="16" r:id="rId12"/>
-    <sheet name="JVM里变量加载图" sheetId="18" r:id="rId13"/>
-    <sheet name="windowbuilder安装" sheetId="19" r:id="rId14"/>
-    <sheet name="１" sheetId="9" state="hidden" r:id="rId15"/>
-    <sheet name="2" sheetId="10" state="hidden" r:id="rId16"/>
-    <sheet name="３" sheetId="11" state="hidden" r:id="rId17"/>
-    <sheet name="４" sheetId="12" state="hidden" r:id="rId18"/>
-    <sheet name="５" sheetId="13" state="hidden" r:id="rId19"/>
-    <sheet name="6" sheetId="14" state="hidden" r:id="rId20"/>
+    <sheet name="Sheet1" sheetId="22" r:id="rId12"/>
+    <sheet name="SQL宿題2" sheetId="16" r:id="rId13"/>
+    <sheet name="JVM里变量加载图" sheetId="18" r:id="rId14"/>
+    <sheet name="windowbuilder安装" sheetId="19" r:id="rId15"/>
+    <sheet name="１" sheetId="9" r:id="rId16"/>
+    <sheet name="2" sheetId="10" r:id="rId17"/>
+    <sheet name="３" sheetId="11" r:id="rId18"/>
+    <sheet name="４" sheetId="12" state="hidden" r:id="rId19"/>
+    <sheet name="５" sheetId="13" state="hidden" r:id="rId20"/>
+    <sheet name="6" sheetId="14" state="hidden" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'ITフレームワーク(４～６ケ月)'!$A$1:$H$38</definedName>
@@ -468,7 +469,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="673">
   <si>
     <t>日付</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -930,9 +931,6 @@
   </si>
   <si>
     <t>TABLE:</t>
-  </si>
-  <si>
-    <t>course_table</t>
   </si>
   <si>
     <t>学科テーブル</t>
@@ -1939,9 +1937,6 @@
   </si>
   <si>
     <t>更新時間</t>
-  </si>
-  <si>
-    <t>更新時間</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2031,9 +2026,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>t_dept</t>
-  </si>
-  <si>
     <t>部門テーブル</t>
   </si>
   <si>
@@ -2049,9 +2041,6 @@
     <t>deptno</t>
   </si>
   <si>
-    <t>dname</t>
-  </si>
-  <si>
     <t>loc</t>
   </si>
   <si>
@@ -2091,9 +2080,6 @@
     <t>情報部</t>
   </si>
   <si>
-    <t>t_emp</t>
-  </si>
-  <si>
     <t>雇員テーブル</t>
   </si>
   <si>
@@ -2115,15 +2101,6 @@
     <t>月給</t>
   </si>
   <si>
-    <t>empno</t>
-  </si>
-  <si>
-    <t>first_nm</t>
-  </si>
-  <si>
-    <t>last_nm</t>
-  </si>
-  <si>
     <t>sex</t>
   </si>
   <si>
@@ -2221,9 +2198,6 @@
   </si>
   <si>
     <t>作业03</t>
-  </si>
-  <si>
-    <t>查询每个部門拠点的人数，并按照人数多少进行降序排序。</t>
   </si>
   <si>
     <t>作业04</t>
@@ -3204,6 +3178,178 @@
 根据行1-44之间的表结构，写出SQL建表语句</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>https://dev.mysql.com/downloads/mysql/</t>
+  </si>
+  <si>
+    <t>s001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>course_table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>score_table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人番号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_002</t>
+  </si>
+  <si>
+    <t>ID_003</t>
+  </si>
+  <si>
+    <t>姓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国民建康保险</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t_dept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t_emp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>查询</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每个部門拠点的人数</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，并按照人数多少进行降序排序。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新潟県</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>first_nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登録日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登録者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>削除フラグ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>０</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>１</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tanaka</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_user_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新時間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部門番号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3212,7 +3358,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;月&quot;dd&quot;日&quot;\(aaa\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3386,8 +3532,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3451,6 +3605,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3827,7 +3987,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -3964,6 +4124,18 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3995,7 +4167,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4009,19 +4181,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="16" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -5742,16 +5905,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>254553</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>217832</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2379</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>107836</xdr:rowOff>
+      <xdr:colOff>681554</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>179619</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5774,8 +5937,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="596900" y="6546850"/>
-          <a:ext cx="6371429" cy="914286"/>
+          <a:off x="1276075" y="17042571"/>
+          <a:ext cx="6368392" cy="1287004"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5788,13 +5951,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>27914</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>28452</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5832,13 +5995,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>580381</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>56976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5883,7 +6046,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>589733</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>85333</xdr:rowOff>
+      <xdr:rowOff>85334</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5964,14 +6127,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>322638</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>114167</xdr:rowOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>114166</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6544,7 +6707,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="49" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="2:4">
@@ -6556,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -6565,10 +6728,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="2:4">
@@ -6580,7 +6743,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -6592,7 +6755,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -6601,10 +6764,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" spans="2:4">
@@ -6616,7 +6779,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -6628,7 +6791,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -6637,10 +6800,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -6652,7 +6815,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="2:4">
@@ -6716,27 +6879,27 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="4:10">
       <c r="D25" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="32" spans="4:10">
       <c r="J32" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -6752,7 +6915,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.4140625" style="15" bestFit="1" customWidth="1"/>
@@ -6768,521 +6931,523 @@
         <v>136</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16">
       <c r="A2" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="18" t="s">
         <v>141</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="18" t="s">
         <v>145</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16">
       <c r="A4" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="D4" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16">
       <c r="A5" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>152</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="16" t="s">
+    </row>
+    <row r="7" spans="1:5" s="97" customFormat="1">
+      <c r="A7" s="96" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="16" t="s">
+      <c r="B7" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="C7" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="96" t="s">
         <v>160</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="C8" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="D8" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+    </row>
+    <row r="9" spans="1:5" hidden="1"/>
+    <row r="10" spans="1:5" hidden="1">
       <c r="A10" s="14" t="s">
         <v>136</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>94</v>
+        <v>638</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" hidden="1">
+      <c r="A11" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="16">
-      <c r="A11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="E11" s="24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" hidden="1">
+      <c r="A12" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16">
-      <c r="A12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="E12" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E12" s="18" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="16" hidden="1">
+      <c r="A13" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="16">
-      <c r="A13" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="17" t="s">
+      <c r="E13" s="18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" hidden="1">
+      <c r="A14" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="18" t="s">
+      <c r="B14" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1">
+      <c r="A15" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1">
+      <c r="A16" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="16">
-      <c r="A14" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="16" t="s">
+      <c r="C16" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1">
+      <c r="A17" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="16" t="s">
+      <c r="D17" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="16" t="s">
+    </row>
+    <row r="18" spans="1:5" hidden="1">
+      <c r="A18" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="16" t="s">
+      <c r="D18" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D18" s="16" t="s">
+      <c r="E18" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" hidden="1">
+      <c r="A19" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="16" t="s">
+      <c r="B19" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="C19" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D19" s="16" t="s">
+      <c r="E19" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1">
+      <c r="A20" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="16" t="s">
+      <c r="B20" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" s="16" t="s">
+      <c r="E20" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" hidden="1">
+      <c r="A21" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E20" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="16" t="s">
+      <c r="B21" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="C21" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="16" t="s">
+      <c r="E21" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1">
+      <c r="A22" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="16" t="s">
+      <c r="B22" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" hidden="1">
+      <c r="A23" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="16" t="s">
+      <c r="B23" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="C23" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="16" t="s">
+      <c r="E23" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="E23" s="16" t="s">
+    </row>
+    <row r="24" spans="1:5" hidden="1">
+      <c r="A24" s="16" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="16" t="s">
-        <v>195</v>
-      </c>
       <c r="B24" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>193</v>
-      </c>
       <c r="E24" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1"/>
+    <row r="26" spans="1:5" hidden="1">
       <c r="A26" s="14" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="14" t="s">
+    </row>
+    <row r="27" spans="1:5" ht="16" hidden="1">
+      <c r="A27" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="18" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="16">
-      <c r="A27" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C27" s="18" t="s">
+      <c r="D27" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="E27" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E27" s="18" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="16" hidden="1">
+      <c r="A28" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C28" s="18" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="16">
-      <c r="A28" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="18" t="s">
+      <c r="D28" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="E28" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="18" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="16" hidden="1">
+      <c r="A29" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="16">
-      <c r="A29" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B29" s="17" t="s">
+      <c r="E29" s="18" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" hidden="1">
+      <c r="A30" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="E29" s="18" t="s">
+      <c r="B30" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1">
+      <c r="A31" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="16">
-      <c r="A30" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="E31" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="16" t="s">
+    </row>
+    <row r="32" spans="1:5" hidden="1">
+      <c r="A32" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="D32" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E32" s="16" t="s">
+    </row>
+    <row r="33" spans="1:5" hidden="1">
+      <c r="A33" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="E33" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="16" t="s">
+    </row>
+    <row r="34" spans="1:5" hidden="1">
+      <c r="A34" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="D34" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E34" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E34" s="16" t="s">
+    </row>
+    <row r="35" spans="1:5" hidden="1">
+      <c r="A35" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="D35" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="16" t="s">
         <v>216</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7290,118 +7455,118 @@
         <v>136</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>218</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16">
       <c r="A38" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D38" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>199</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16">
       <c r="A39" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C39" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D39" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="E39" s="18" t="s">
         <v>222</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16">
       <c r="A40" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D40" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="E40" s="18" t="s">
         <v>204</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16">
       <c r="A41" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B41" s="17" t="s">
-        <v>152</v>
-      </c>
       <c r="C41" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C42" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E42" s="16" t="s">
         <v>224</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C43" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="16" t="s">
         <v>226</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:5" s="22" customFormat="1" ht="21"/>
     <row r="47" spans="1:5" s="22" customFormat="1" ht="21">
       <c r="B47" s="22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:5" s="22" customFormat="1" ht="21"/>
@@ -7412,7 +7577,7 @@
     <row r="53" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="54" spans="2:2" s="22" customFormat="1" ht="21">
       <c r="B54" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="2:2" s="22" customFormat="1" ht="21"/>
@@ -7428,28 +7593,24 @@
     <row r="65" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="66" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="67" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="68" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B68" s="22" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B69" s="22" t="s">
-        <v>295</v>
-      </c>
-    </row>
+    <row r="68" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="69" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="70" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="71" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="72" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="73" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="74" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="75" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="74" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B74" s="22" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B75" s="22" t="s">
+        <v>294</v>
+      </c>
+    </row>
     <row r="76" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="77" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B77" s="22" t="s">
-        <v>296</v>
-      </c>
-    </row>
+    <row r="77" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="78" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="79" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="80" spans="2:2" s="22" customFormat="1" ht="21"/>
@@ -7457,7 +7618,7 @@
     <row r="82" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="83" spans="2:2" s="22" customFormat="1" ht="21">
       <c r="B83" s="22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="2:2" s="22" customFormat="1" ht="21"/>
@@ -7465,556 +7626,750 @@
     <row r="86" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="87" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="88" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="89" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="89" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B89" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
     <row r="90" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="91" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="92" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="93" spans="2:2" s="22" customFormat="1" ht="21">
-      <c r="B93" s="22" t="s">
-        <v>298</v>
-      </c>
-    </row>
+    <row r="93" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="94" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="95" spans="2:2" s="22" customFormat="1" ht="21"/>
     <row r="96" spans="2:2" s="22" customFormat="1" ht="21"/>
-    <row r="97" s="22" customFormat="1" ht="21"/>
-    <row r="98" s="22" customFormat="1" ht="21"/>
-    <row r="99" s="22" customFormat="1" ht="21"/>
+    <row r="97" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="98" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="99" spans="2:2" s="22" customFormat="1" ht="21">
+      <c r="B99" s="22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="101" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="102" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="103" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="104" spans="2:2" s="22" customFormat="1" ht="21"/>
+    <row r="105" spans="2:2" s="22" customFormat="1" ht="21"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7DDDE3-BD4E-47A6-BA24-BE0A22022D1B}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="B3:E17"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="12.4140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5">
+      <c r="B3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" t="s">
+        <v>584</v>
+      </c>
+      <c r="D4" t="s">
+        <v>643</v>
+      </c>
+      <c r="E4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="C5" t="s">
+        <v>640</v>
+      </c>
+      <c r="D5" t="s">
+        <v>645</v>
+      </c>
+      <c r="E5" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="C6" t="s">
+        <v>641</v>
+      </c>
+      <c r="D6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E6" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="C7" t="s">
+        <v>642</v>
+      </c>
+      <c r="D7" t="s">
+        <v>645</v>
+      </c>
+      <c r="E7" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="C10" t="s">
+        <v>584</v>
+      </c>
+      <c r="D10" t="s">
+        <v>643</v>
+      </c>
+      <c r="E10" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D11" t="s">
+        <v>645</v>
+      </c>
+      <c r="E11" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="C12" t="s">
+        <v>642</v>
+      </c>
+      <c r="D12" t="s">
+        <v>645</v>
+      </c>
+      <c r="E12" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" t="s">
+        <v>584</v>
+      </c>
+      <c r="D15" t="s">
+        <v>643</v>
+      </c>
+      <c r="E15" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="C16" t="s">
+        <v>640</v>
+      </c>
+      <c r="D16" t="s">
+        <v>645</v>
+      </c>
+      <c r="E16" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" t="s">
+        <v>641</v>
+      </c>
+      <c r="D17" t="s">
+        <v>645</v>
+      </c>
+      <c r="E17" t="s">
+        <v>647</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CA0124-BB09-4A5F-B469-7554949501A3}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="15"/>
+    <col min="2" max="2" width="29.83203125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="9" style="15"/>
+    <col min="4" max="4" width="19.08203125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="9" style="15"/>
+    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="11.4140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="15" customWidth="1"/>
+    <col min="9" max="10" width="9" style="15"/>
+    <col min="11" max="11" width="15.08203125" style="15" customWidth="1"/>
+    <col min="12" max="12" width="15.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16">
+      <c r="A2" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16">
+      <c r="A3" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16">
+      <c r="A4" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16">
+      <c r="A5" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>652</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16">
+      <c r="A12" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>672</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>671</v>
+      </c>
+      <c r="K12" s="114" t="s">
+        <v>659</v>
+      </c>
+      <c r="L12" s="114" t="s">
+        <v>660</v>
+      </c>
+      <c r="M12" s="114" t="s">
+        <v>661</v>
+      </c>
+      <c r="N12" s="114" t="s">
+        <v>662</v>
+      </c>
+      <c r="O12" s="114" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16">
+      <c r="A13" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>654</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>656</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>658</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16">
+      <c r="A14" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>667</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>666</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16">
+      <c r="A15" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="J16" s="16"/>
+      <c r="O16" s="15" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="J17" s="16"/>
+      <c r="O17" s="15" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="B22" s="27" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="27" customFormat="1">
+      <c r="A25" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="B32" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CA0124-BB09-4A5F-B469-7554949501A3}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="16384" width="9" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16">
-      <c r="A2" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16">
-      <c r="A3" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="16">
-      <c r="A4" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="16">
-      <c r="A5" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="16">
-      <c r="A12" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>414</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16">
-      <c r="A13" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>420</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16">
-      <c r="A14" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16">
-      <c r="A15" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>426</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>468</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>437</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>438</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>442</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>443</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="B24" s="27" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="B34" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>469</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A7714B-D9DD-416F-B392-2E2CEF359F1C}">
   <sheetPr>
     <tabColor theme="7"/>
@@ -8029,7 +8384,7 @@
   <sheetData>
     <row r="2" spans="3:26">
       <c r="F2" s="52" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="3:26">
@@ -8054,19 +8409,19 @@
     </row>
     <row r="5" spans="3:26">
       <c r="U5" s="75" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="V5" s="75" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="W5" s="75" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="X5" s="75" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="Y5" s="75" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="14.5" thickBot="1"/>
@@ -8101,7 +8456,7 @@
       <c r="D8" s="57"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="57"/>
@@ -8115,14 +8470,14 @@
       <c r="P8" s="57"/>
       <c r="Q8" s="57"/>
       <c r="R8" s="57" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="S8" s="57"/>
       <c r="T8" s="57"/>
       <c r="U8" s="78"/>
       <c r="V8" s="78"/>
       <c r="W8" s="78" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="X8" s="78"/>
       <c r="Y8" s="78"/>
@@ -8133,7 +8488,7 @@
       <c r="D9" s="57"/>
       <c r="E9" s="58"/>
       <c r="F9" s="62" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="G9" s="63"/>
       <c r="H9" s="63"/>
@@ -8188,16 +8543,16 @@
       <c r="E11" s="58"/>
       <c r="F11" s="65"/>
       <c r="G11" s="68" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="H11" s="68" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="I11" s="68" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="J11" s="68" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="K11" s="63"/>
       <c r="L11" s="63"/>
@@ -8249,10 +8604,10 @@
       <c r="G13" s="69"/>
       <c r="H13" s="69"/>
       <c r="I13" s="69" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="J13" s="69" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="K13" s="66"/>
       <c r="L13" s="66"/>
@@ -8279,7 +8634,7 @@
       <c r="G14" s="69"/>
       <c r="H14" s="69"/>
       <c r="I14" s="69" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="J14" s="69"/>
       <c r="K14" s="66"/>
@@ -8328,7 +8683,7 @@
     <row r="16" spans="3:26" ht="14.5" thickBot="1">
       <c r="C16" s="56"/>
       <c r="D16" s="57" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E16" s="58"/>
       <c r="F16" s="65"/>
@@ -8384,13 +8739,13 @@
       <c r="D18" s="57"/>
       <c r="E18" s="58"/>
       <c r="F18" s="56" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="G18" s="57"/>
       <c r="H18" s="57"/>
       <c r="I18" s="57"/>
       <c r="J18" s="53" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="K18" s="54"/>
       <c r="L18" s="54"/>
@@ -8414,14 +8769,14 @@
       <c r="D19" s="57"/>
       <c r="E19" s="58"/>
       <c r="F19" s="56" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="G19" s="57"/>
       <c r="H19" s="57"/>
       <c r="I19" s="57"/>
       <c r="J19" s="56"/>
       <c r="K19" s="57" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="L19" s="57"/>
       <c r="M19" s="57"/>
@@ -8444,7 +8799,7 @@
       <c r="D20" s="57"/>
       <c r="E20" s="58"/>
       <c r="F20" s="56" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="G20" s="57"/>
       <c r="H20" s="57"/>
@@ -8472,7 +8827,7 @@
       <c r="D21" s="57"/>
       <c r="E21" s="58"/>
       <c r="F21" s="56" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="G21" s="57"/>
       <c r="H21" s="57"/>
@@ -8500,7 +8855,7 @@
       <c r="D22" s="57"/>
       <c r="E22" s="58"/>
       <c r="F22" s="56" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="G22" s="57"/>
       <c r="H22" s="57"/>
@@ -8528,7 +8883,7 @@
       <c r="D23" s="57"/>
       <c r="E23" s="58"/>
       <c r="F23" s="56" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="G23" s="57"/>
       <c r="H23" s="57"/>
@@ -8556,7 +8911,7 @@
       <c r="D24" s="57"/>
       <c r="E24" s="58"/>
       <c r="F24" s="56" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="G24" s="57"/>
       <c r="H24" s="57"/>
@@ -8584,7 +8939,7 @@
       <c r="D25" s="57"/>
       <c r="E25" s="58"/>
       <c r="F25" s="56" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="G25" s="57"/>
       <c r="H25" s="57"/>
@@ -8612,7 +8967,7 @@
       <c r="D26" s="57"/>
       <c r="E26" s="58"/>
       <c r="F26" s="59" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="G26" s="60"/>
       <c r="H26" s="60"/>
@@ -8668,7 +9023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41AFFA43-4820-4AD6-9E6A-7F8B8CFA34B7}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -8678,7 +9033,7 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="42" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -8691,7 +9046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF30867F-4987-428B-B1BA-79BEE1AC7E24}">
   <dimension ref="B1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8702,7 +9057,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="16">
       <c r="B1" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:15">
@@ -8712,12 +9067,12 @@
     </row>
     <row r="4" spans="2:15">
       <c r="O4" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="O5" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="2:15">
@@ -8727,12 +9082,12 @@
     </row>
     <row r="7" spans="2:15">
       <c r="O7" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="O8" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="2:15">
@@ -8742,7 +9097,7 @@
     </row>
     <row r="10" spans="2:15">
       <c r="O10" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="2:15">
@@ -8752,7 +9107,7 @@
     </row>
     <row r="12" spans="2:15">
       <c r="O12" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -8762,7 +9117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D3055-B4C0-44F8-BC38-3332800489E4}">
   <dimension ref="B1:S32"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8772,7 +9127,7 @@
   <sheetData>
     <row r="1" spans="2:19" ht="16">
       <c r="B1" s="23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="2:19">
@@ -8782,17 +9137,17 @@
     </row>
     <row r="3" spans="2:19">
       <c r="S3" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="2:19">
       <c r="S4" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="2:19">
       <c r="S5" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -8802,102 +9157,102 @@
     </row>
     <row r="7" spans="2:19">
       <c r="S7" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="2:19">
       <c r="S8" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="2:19">
       <c r="S9" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="2:19">
       <c r="S10" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="2:19">
       <c r="S11" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="2:19">
       <c r="S12" s="20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="S13" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="2:19">
       <c r="S14" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="S15" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="2:19">
       <c r="S16" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="19:19">
       <c r="S17" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="19:19">
       <c r="S18" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="19:19">
       <c r="S19" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="19:19">
       <c r="S20" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="19:19">
       <c r="S21" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="19:19">
       <c r="S22" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" spans="19:19">
       <c r="S23" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="19:19">
       <c r="S24" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="19:19">
       <c r="S25" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="19:19">
       <c r="S26" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" spans="19:19">
@@ -8907,27 +9262,27 @@
     </row>
     <row r="28" spans="19:19">
       <c r="S28" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="19:19">
       <c r="S29" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="19:19">
       <c r="S30" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="19:19">
       <c r="S31" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="19:19">
       <c r="S32" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -8937,7 +9292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBA7452-ADCF-4916-B20B-0512AE3ED3F2}">
   <dimension ref="B1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8948,12 +9303,12 @@
   <sheetData>
     <row r="1" spans="2:14" ht="16">
       <c r="B1" s="23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="2:14" ht="16">
       <c r="B2" s="23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N2" s="20" t="s">
         <v>45</v>
@@ -8961,12 +9316,12 @@
     </row>
     <row r="3" spans="2:14">
       <c r="N3" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="N4" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="2:14">
@@ -8976,17 +9331,17 @@
     </row>
     <row r="6" spans="2:14">
       <c r="N6" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="2:14">
       <c r="N7" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="N8" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="2:14">
@@ -8996,7 +9351,7 @@
     </row>
     <row r="10" spans="2:14">
       <c r="N10" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -9006,7 +9361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A228C4-8BB0-42F2-86E2-63F3E8493370}">
   <dimension ref="B1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9017,7 +9372,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="16">
       <c r="B1" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="2:15">
@@ -9027,7 +9382,7 @@
     </row>
     <row r="3" spans="2:15">
       <c r="O3" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -9037,17 +9392,17 @@
     </row>
     <row r="5" spans="2:15">
       <c r="O5" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="O6" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="2:15">
       <c r="O7" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -9057,62 +9412,7 @@
     </row>
     <row r="9" spans="2:15">
       <c r="O9" s="20" t="s">
-        <v>337</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C125254-9191-4F9A-8C38-B14BF103FA27}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="16384" width="8.6640625" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="16">
-      <c r="A1" s="23" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="N2" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="N3" s="20" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="N4" s="20" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="N5" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="N6" s="20" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="N7" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="N8" s="20" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -9132,67 +9432,67 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="43" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="42" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="43" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" s="41" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="41" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="41" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="42" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="41" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -9206,6 +9506,61 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C125254-9191-4F9A-8C38-B14BF103FA27}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="8.6640625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="16">
+      <c r="A1" s="23" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="N2" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="N3" s="20" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="N4" s="20" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="N5" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="N6" s="20" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="N7" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="N8" s="20" t="s">
+        <v>341</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E4EC444-DA0C-43AC-8DA7-D83AAF18CFD5}">
   <dimension ref="B1:S26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9216,7 +9571,7 @@
   <sheetData>
     <row r="1" spans="2:19" ht="16">
       <c r="B1" s="23" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="2:19" ht="16">
@@ -9229,7 +9584,7 @@
     </row>
     <row r="4" spans="2:19">
       <c r="R4" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="2:19">
@@ -9239,97 +9594,97 @@
     </row>
     <row r="6" spans="2:19">
       <c r="R6" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="2:19">
       <c r="R7" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="2:19">
       <c r="R8" s="20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="2:19">
       <c r="R9" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="2:19">
       <c r="R10" s="20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="2:19">
       <c r="R11" s="20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="2:19">
       <c r="R12" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="R13" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="2:19">
       <c r="R14" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="R15" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="2:19">
       <c r="S16" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="18:18">
       <c r="R17" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="18:18">
       <c r="R18" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="18:18">
       <c r="R19" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="18:18">
       <c r="R20" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="18:18">
       <c r="R21" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="18:18">
       <c r="R22" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" spans="18:18">
       <c r="R23" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="18:18">
       <c r="R24" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" spans="18:18">
@@ -9339,7 +9694,7 @@
     </row>
     <row r="26" spans="18:18">
       <c r="R26" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -9381,7 +9736,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>5</v>
@@ -9391,7 +9746,7 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="98" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6">
@@ -9410,7 +9765,7 @@
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="92" t="s">
+      <c r="H3" s="102" t="s">
         <v>14</v>
       </c>
       <c r="J3" s="33">
@@ -9418,7 +9773,7 @@
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="89"/>
+      <c r="B4" s="99"/>
       <c r="C4" s="6">
         <f>$J$3</f>
         <v>44598</v>
@@ -9435,10 +9790,10 @@
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="93"/>
+      <c r="H4" s="103"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="89"/>
+      <c r="B5" s="99"/>
       <c r="C5" s="6">
         <f>$J$3</f>
         <v>44598</v>
@@ -9455,10 +9810,10 @@
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="93"/>
+      <c r="H5" s="103"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="89"/>
+      <c r="B6" s="99"/>
       <c r="C6" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -9475,12 +9830,12 @@
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="92" t="s">
+      <c r="H6" s="102" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="89"/>
+      <c r="B7" s="99"/>
       <c r="C7" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -9497,10 +9852,10 @@
       <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="93"/>
+      <c r="H7" s="103"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="89"/>
+      <c r="B8" s="99"/>
       <c r="C8" s="6">
         <f>$J$3+7</f>
         <v>44605</v>
@@ -9517,10 +9872,10 @@
       <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="93"/>
+      <c r="H8" s="103"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="89"/>
+      <c r="B9" s="99"/>
       <c r="C9" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -9537,12 +9892,12 @@
       <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="93" t="s">
+      <c r="H9" s="103" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="89"/>
+      <c r="B10" s="99"/>
       <c r="C10" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -9559,10 +9914,10 @@
       <c r="G10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="93"/>
+      <c r="H10" s="103"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="89"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="6">
         <f>$J$3+14</f>
         <v>44612</v>
@@ -9579,10 +9934,10 @@
       <c r="G11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="93"/>
+      <c r="H11" s="103"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="89"/>
+      <c r="B12" s="99"/>
       <c r="C12" s="6">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -9599,12 +9954,12 @@
       <c r="G12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="92" t="s">
-        <v>498</v>
+      <c r="H12" s="102" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="89"/>
+      <c r="B13" s="99"/>
       <c r="C13" s="6">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -9621,10 +9976,10 @@
       <c r="G13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="93"/>
+      <c r="H13" s="103"/>
     </row>
     <row r="14" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B14" s="90"/>
+      <c r="B14" s="100"/>
       <c r="C14" s="28">
         <f>$J$3+21</f>
         <v>44619</v>
@@ -9641,10 +9996,10 @@
       <c r="G14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="94"/>
+      <c r="H14" s="104"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="101" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="29">
@@ -9661,9 +10016,9 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="H15" s="95" t="s">
+        <v>499</v>
+      </c>
+      <c r="H15" s="105" t="s">
         <v>42</v>
       </c>
       <c r="J15" s="33">
@@ -9671,7 +10026,7 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="89"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="6">
         <f>$J$15</f>
         <v>44626</v>
@@ -9686,12 +10041,12 @@
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="H16" s="93"/>
+        <v>498</v>
+      </c>
+      <c r="H16" s="103"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="89"/>
+      <c r="B17" s="99"/>
       <c r="C17" s="6">
         <f>$J$15</f>
         <v>44626</v>
@@ -9706,12 +10061,12 @@
         <v>3</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H17" s="93"/>
+        <v>382</v>
+      </c>
+      <c r="H17" s="103"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="89"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -9728,12 +10083,12 @@
       <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="96" t="s">
+      <c r="H18" s="106" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="89"/>
+      <c r="B19" s="99"/>
       <c r="C19" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -9750,10 +10105,10 @@
       <c r="G19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="93"/>
+      <c r="H19" s="103"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="89"/>
+      <c r="B20" s="99"/>
       <c r="C20" s="6">
         <f>$J$15+7</f>
         <v>44633</v>
@@ -9770,10 +10125,10 @@
       <c r="G20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="93"/>
+      <c r="H20" s="103"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="89"/>
+      <c r="B21" s="99"/>
       <c r="C21" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -9790,12 +10145,12 @@
       <c r="G21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="93" t="s">
-        <v>385</v>
+      <c r="H21" s="103" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="89"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -9812,10 +10167,10 @@
       <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="93"/>
+      <c r="H22" s="103"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="89"/>
+      <c r="B23" s="99"/>
       <c r="C23" s="6">
         <f>$J$15+14</f>
         <v>44640</v>
@@ -9832,10 +10187,10 @@
       <c r="G23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="93"/>
+      <c r="H23" s="103"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="89"/>
+      <c r="B24" s="99"/>
       <c r="C24" s="6">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -9852,12 +10207,12 @@
       <c r="G24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="93" t="s">
-        <v>381</v>
+      <c r="H24" s="103" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="89"/>
+      <c r="B25" s="99"/>
       <c r="C25" s="6">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -9874,10 +10229,10 @@
       <c r="G25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="93"/>
+      <c r="H25" s="103"/>
     </row>
     <row r="26" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B26" s="90"/>
+      <c r="B26" s="100"/>
       <c r="C26" s="30">
         <f>$J$15+21</f>
         <v>44647</v>
@@ -9894,10 +10249,10 @@
       <c r="G26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="97"/>
+      <c r="H26" s="107"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="101" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="31">
@@ -9916,15 +10271,15 @@
       <c r="G27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="111" t="s">
-        <v>643</v>
+      <c r="H27" s="108" t="s">
+        <v>634</v>
       </c>
       <c r="J27" s="33">
         <v>44654</v>
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="89"/>
+      <c r="B28" s="99"/>
       <c r="C28" s="6">
         <f>$J$27</f>
         <v>44654</v>
@@ -9941,10 +10296,10 @@
       <c r="G28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="93"/>
+      <c r="H28" s="103"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="89"/>
+      <c r="B29" s="99"/>
       <c r="C29" s="6">
         <f>$J$27</f>
         <v>44654</v>
@@ -9961,10 +10316,10 @@
       <c r="G29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="93"/>
+      <c r="H29" s="103"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="89"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -9981,12 +10336,12 @@
       <c r="G30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="93" t="s">
-        <v>510</v>
+      <c r="H30" s="103" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="89"/>
+      <c r="B31" s="99"/>
       <c r="C31" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -10003,10 +10358,10 @@
       <c r="G31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H31" s="93"/>
+      <c r="H31" s="103"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="89"/>
+      <c r="B32" s="99"/>
       <c r="C32" s="6">
         <f>$J$27+7</f>
         <v>44661</v>
@@ -10023,10 +10378,10 @@
       <c r="G32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H32" s="93"/>
+      <c r="H32" s="103"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="89"/>
+      <c r="B33" s="99"/>
       <c r="C33" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -10043,12 +10398,12 @@
       <c r="G33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="92" t="s">
-        <v>511</v>
+      <c r="H33" s="102" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="89"/>
+      <c r="B34" s="99"/>
       <c r="C34" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -10065,10 +10420,10 @@
       <c r="G34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H34" s="93"/>
+      <c r="H34" s="103"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="89"/>
+      <c r="B35" s="99"/>
       <c r="C35" s="6">
         <f>$J$27+14</f>
         <v>44668</v>
@@ -10085,10 +10440,10 @@
       <c r="G35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H35" s="93"/>
+      <c r="H35" s="103"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="89"/>
+      <c r="B36" s="99"/>
       <c r="C36" s="6">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -10103,14 +10458,14 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="H36" s="92" t="s">
-        <v>512</v>
+        <v>461</v>
+      </c>
+      <c r="H36" s="102" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="89"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="6">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -10127,10 +10482,10 @@
       <c r="G37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="93"/>
+      <c r="H37" s="103"/>
     </row>
     <row r="38" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B38" s="90"/>
+      <c r="B38" s="100"/>
       <c r="C38" s="28">
         <f>$J$27+21</f>
         <v>44675</v>
@@ -10147,7 +10502,7 @@
       <c r="G38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="94"/>
+      <c r="H38" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -10208,7 +10563,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>4</v>
@@ -10218,8 +10573,8 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="88" t="s">
-        <v>476</v>
+      <c r="B3" s="98" t="s">
+        <v>467</v>
       </c>
       <c r="C3" s="6">
         <f>$J$3</f>
@@ -10237,15 +10592,15 @@
       <c r="G3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="92" t="s">
-        <v>503</v>
+      <c r="H3" s="102" t="s">
+        <v>494</v>
       </c>
       <c r="J3" s="33">
         <v>44689</v>
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="99"/>
+      <c r="B4" s="109"/>
       <c r="C4" s="6">
         <f>$J$3</f>
         <v>44689</v>
@@ -10262,10 +10617,10 @@
       <c r="G4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="93"/>
+      <c r="H4" s="103"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="99"/>
+      <c r="B5" s="109"/>
       <c r="C5" s="6">
         <f>$J$3</f>
         <v>44689</v>
@@ -10282,10 +10637,10 @@
       <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="93"/>
+      <c r="H5" s="103"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="99"/>
+      <c r="B6" s="109"/>
       <c r="C6" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -10300,14 +10655,14 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="H6" s="92" t="s">
-        <v>471</v>
+        <v>464</v>
+      </c>
+      <c r="H6" s="102" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="99"/>
+      <c r="B7" s="109"/>
       <c r="C7" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -10322,12 +10677,12 @@
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="H7" s="93"/>
+        <v>464</v>
+      </c>
+      <c r="H7" s="103"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="99"/>
+      <c r="B8" s="109"/>
       <c r="C8" s="6">
         <f>$J$3+7</f>
         <v>44696</v>
@@ -10342,12 +10697,12 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="H8" s="93"/>
+        <v>464</v>
+      </c>
+      <c r="H8" s="103"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="99"/>
+      <c r="B9" s="109"/>
       <c r="C9" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -10362,12 +10717,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="H9" s="93"/>
+        <v>463</v>
+      </c>
+      <c r="H9" s="103"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="99"/>
+      <c r="B10" s="109"/>
       <c r="C10" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -10382,12 +10737,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="H10" s="93"/>
+        <v>463</v>
+      </c>
+      <c r="H10" s="103"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="99"/>
+      <c r="B11" s="109"/>
       <c r="C11" s="6">
         <f>$J$3+14</f>
         <v>44703</v>
@@ -10404,10 +10759,10 @@
       <c r="G11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="93"/>
+      <c r="H11" s="103"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="99"/>
+      <c r="B12" s="109"/>
       <c r="C12" s="6">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -10424,10 +10779,10 @@
       <c r="G12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="93"/>
+      <c r="H12" s="103"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="99"/>
+      <c r="B13" s="109"/>
       <c r="C13" s="6">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -10444,10 +10799,10 @@
       <c r="G13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="93"/>
+      <c r="H13" s="103"/>
     </row>
     <row r="14" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B14" s="99"/>
+      <c r="B14" s="109"/>
       <c r="C14" s="28">
         <f>$J$3+21</f>
         <v>44710</v>
@@ -10464,10 +10819,10 @@
       <c r="G14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="94"/>
+      <c r="H14" s="104"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="99"/>
+      <c r="B15" s="109"/>
       <c r="C15" s="29">
         <f>$J$15</f>
         <v>44717</v>
@@ -10484,13 +10839,13 @@
       <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="102"/>
+      <c r="H15" s="112"/>
       <c r="J15" s="33">
         <v>44717</v>
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="99"/>
+      <c r="B16" s="109"/>
       <c r="C16" s="6">
         <f>$J$15</f>
         <v>44717</v>
@@ -10507,10 +10862,10 @@
       <c r="G16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="93"/>
+      <c r="H16" s="103"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="99"/>
+      <c r="B17" s="109"/>
       <c r="C17" s="6">
         <f>$J$15</f>
         <v>44717</v>
@@ -10527,10 +10882,10 @@
       <c r="G17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="93"/>
+      <c r="H17" s="103"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="99"/>
+      <c r="B18" s="109"/>
       <c r="C18" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -10547,10 +10902,10 @@
       <c r="G18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="93"/>
+      <c r="H18" s="103"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="99"/>
+      <c r="B19" s="109"/>
       <c r="C19" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -10567,10 +10922,10 @@
       <c r="G19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="93"/>
+      <c r="H19" s="103"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="99"/>
+      <c r="B20" s="109"/>
       <c r="C20" s="6">
         <f>$J$15+7</f>
         <v>44724</v>
@@ -10587,10 +10942,10 @@
       <c r="G20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="93"/>
+      <c r="H20" s="103"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="99"/>
+      <c r="B21" s="109"/>
       <c r="C21" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -10607,10 +10962,10 @@
       <c r="G21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="93"/>
+      <c r="H21" s="103"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="99"/>
+      <c r="B22" s="109"/>
       <c r="C22" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -10627,10 +10982,10 @@
       <c r="G22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="93"/>
+      <c r="H22" s="103"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="99"/>
+      <c r="B23" s="109"/>
       <c r="C23" s="6">
         <f>$J$15+14</f>
         <v>44731</v>
@@ -10647,10 +11002,10 @@
       <c r="G23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="93"/>
+      <c r="H23" s="103"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="99"/>
+      <c r="B24" s="109"/>
       <c r="C24" s="6">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -10667,10 +11022,10 @@
       <c r="G24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="93"/>
+      <c r="H24" s="103"/>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="99"/>
+      <c r="B25" s="109"/>
       <c r="C25" s="6">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -10687,10 +11042,10 @@
       <c r="G25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="93"/>
+      <c r="H25" s="103"/>
     </row>
     <row r="26" spans="2:10" ht="14.5" thickBot="1">
-      <c r="B26" s="100"/>
+      <c r="B26" s="110"/>
       <c r="C26" s="30">
         <f>$J$15+21</f>
         <v>44738</v>
@@ -10707,11 +11062,11 @@
       <c r="G26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="97"/>
+      <c r="H26" s="107"/>
     </row>
     <row r="27" spans="2:10" ht="14" customHeight="1">
-      <c r="B27" s="101" t="s">
-        <v>475</v>
+      <c r="B27" s="111" t="s">
+        <v>466</v>
       </c>
       <c r="C27" s="31">
         <f>$J$27</f>
@@ -10729,15 +11084,15 @@
       <c r="G27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="98" t="s">
-        <v>504</v>
+      <c r="H27" s="113" t="s">
+        <v>495</v>
       </c>
       <c r="J27" s="33">
         <v>44745</v>
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="99"/>
+      <c r="B28" s="109"/>
       <c r="C28" s="6">
         <f>$J$27</f>
         <v>44745</v>
@@ -10754,10 +11109,10 @@
       <c r="G28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="93"/>
+      <c r="H28" s="103"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="99"/>
+      <c r="B29" s="109"/>
       <c r="C29" s="6">
         <f>$J$27</f>
         <v>44745</v>
@@ -10774,10 +11129,10 @@
       <c r="G29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="93"/>
+      <c r="H29" s="103"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="99"/>
+      <c r="B30" s="109"/>
       <c r="C30" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -10792,14 +11147,14 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="H30" s="93" t="s">
-        <v>506</v>
+        <v>496</v>
+      </c>
+      <c r="H30" s="103" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="99"/>
+      <c r="B31" s="109"/>
       <c r="C31" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -10814,12 +11169,12 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="H31" s="93"/>
+        <v>496</v>
+      </c>
+      <c r="H31" s="103"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="99"/>
+      <c r="B32" s="109"/>
       <c r="C32" s="6">
         <f>$J$27+7</f>
         <v>44752</v>
@@ -10834,13 +11189,13 @@
         <v>3</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="H32" s="93"/>
+        <v>496</v>
+      </c>
+      <c r="H32" s="103"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="99" t="s">
-        <v>513</v>
+      <c r="B33" s="109" t="s">
+        <v>504</v>
       </c>
       <c r="C33" s="6">
         <f>$J$27+14</f>
@@ -10858,10 +11213,10 @@
       <c r="G33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="93"/>
+      <c r="H33" s="103"/>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="99"/>
+      <c r="B34" s="109"/>
       <c r="C34" s="6">
         <f>$J$27+14</f>
         <v>44759</v>
@@ -10878,10 +11233,10 @@
       <c r="G34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="93"/>
+      <c r="H34" s="103"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="99"/>
+      <c r="B35" s="109"/>
       <c r="C35" s="6">
         <f>$J$27+14</f>
         <v>44759</v>
@@ -10898,11 +11253,11 @@
       <c r="G35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H35" s="93"/>
+      <c r="H35" s="103"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="99" t="s">
-        <v>514</v>
+      <c r="B36" s="109" t="s">
+        <v>505</v>
       </c>
       <c r="C36" s="6">
         <f>$J$27+21</f>
@@ -10918,12 +11273,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="H36" s="93"/>
+        <v>493</v>
+      </c>
+      <c r="H36" s="103"/>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="89"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="6">
         <f>$J$27+21</f>
         <v>44766</v>
@@ -10938,12 +11293,12 @@
         <v>2</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="H37" s="93"/>
+        <v>492</v>
+      </c>
+      <c r="H37" s="103"/>
     </row>
     <row r="38" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B38" s="90"/>
+      <c r="B38" s="100"/>
       <c r="C38" s="28">
         <f>$J$27+21</f>
         <v>44766</v>
@@ -10958,9 +11313,9 @@
         <v>3</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="H38" s="94"/>
+        <v>492</v>
+      </c>
+      <c r="H38" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -10995,171 +11350,176 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A70:U107"/>
+  <dimension ref="A2:U107"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>635</v>
+      </c>
+    </row>
     <row r="70" spans="2:21" ht="15.5">
       <c r="B70" s="11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="72" spans="2:21" ht="15.5">
       <c r="B72" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="73" spans="2:21" ht="15.5">
       <c r="B73" s="11" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="U73" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="74" spans="2:21" ht="15.5">
       <c r="B74" s="11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15.5">
       <c r="B75" s="11" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="76" spans="2:21" ht="15.5">
       <c r="B76" s="11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" spans="2:21" ht="15.5">
       <c r="B77" s="11" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="U77" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="78" spans="2:21" ht="15.5">
       <c r="B78" s="11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="2:21" ht="15.5">
       <c r="B79" s="11" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="U79" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="80" spans="2:21" ht="15.5">
       <c r="B80" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="81" spans="2:21" ht="15.5">
       <c r="B81" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="82" spans="2:21" ht="15.5">
       <c r="B82" s="11" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="U82" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
     </row>
     <row r="83" spans="2:21" ht="15.5">
       <c r="B83" s="11" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="U83" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
     </row>
     <row r="84" spans="2:21" ht="15.5">
       <c r="B84" s="11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85" spans="2:21" ht="15.5">
       <c r="B85" s="11" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="86" spans="2:21" ht="15.5">
       <c r="B86" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" spans="2:21" ht="15.5">
       <c r="B87" s="11" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="88" spans="2:21" ht="15.5">
       <c r="B88" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="2:21" ht="15.5">
       <c r="B89" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="90" spans="2:21" ht="15.5">
       <c r="B90" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="91" spans="2:21" ht="15.5">
       <c r="B91" s="11" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" spans="2:21" ht="15.5">
       <c r="B92" s="11" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="U92" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="93" spans="2:21" ht="15.5">
       <c r="B93" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" spans="2:21" ht="15.5">
       <c r="B94" s="11" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15.5">
       <c r="B95" s="11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="U95" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="100" spans="1:4" s="85" customFormat="1">
       <c r="A100" s="85" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="B102" s="87" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D102" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="107" spans="1:4" s="85" customFormat="1">
       <c r="A107" s="86" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -11181,214 +11541,215 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="B2" s="43" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="D6" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="C7" t="s">
-        <v>627</v>
-      </c>
-      <c r="D7" s="105" t="s">
-        <v>616</v>
-      </c>
-      <c r="E7" s="105" t="s">
-        <v>617</v>
-      </c>
-      <c r="F7" s="105"/>
+        <v>618</v>
+      </c>
+      <c r="D7" s="90" t="s">
+        <v>607</v>
+      </c>
+      <c r="E7" s="90" t="s">
+        <v>608</v>
+      </c>
+      <c r="F7" s="90"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="D8" s="105" t="s">
-        <v>619</v>
-      </c>
-      <c r="E8" s="105" t="s">
-        <v>620</v>
-      </c>
-      <c r="F8" s="105"/>
+      <c r="D8" s="90" t="s">
+        <v>610</v>
+      </c>
+      <c r="E8" s="90" t="s">
+        <v>611</v>
+      </c>
+      <c r="F8" s="90"/>
     </row>
     <row r="9" spans="2:6">
-      <c r="D9" s="105" t="s">
-        <v>621</v>
-      </c>
-      <c r="E9" s="105" t="s">
-        <v>622</v>
-      </c>
-      <c r="F9" s="105"/>
+      <c r="D9" s="90" t="s">
+        <v>612</v>
+      </c>
+      <c r="E9" s="90" t="s">
+        <v>613</v>
+      </c>
+      <c r="F9" s="90"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="D10" s="105" t="s">
-        <v>623</v>
-      </c>
-      <c r="E10" s="105" t="s">
-        <v>624</v>
-      </c>
-      <c r="F10" s="105"/>
+      <c r="D10" s="90" t="s">
+        <v>614</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>615</v>
+      </c>
+      <c r="F10" s="90"/>
     </row>
     <row r="11" spans="2:6">
       <c r="C11" t="s">
-        <v>628</v>
-      </c>
-      <c r="D11" s="108" t="s">
+        <v>619</v>
+      </c>
+      <c r="D11" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="D12" s="108" t="s">
-        <v>625</v>
-      </c>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
+      <c r="D12" s="93" t="s">
+        <v>616</v>
+      </c>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="D13" s="108" t="s">
-        <v>626</v>
-      </c>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
+      <c r="D13" s="93" t="s">
+        <v>617</v>
+      </c>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="43" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="2:6">
       <c r="C16" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="43" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="C24" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="34" spans="2:11">
       <c r="B34" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
     </row>
     <row r="35" spans="2:11">
-      <c r="D35" s="109" t="s">
+      <c r="D35" s="94" t="s">
+        <v>607</v>
+      </c>
+      <c r="E35" s="94" t="s">
+        <v>610</v>
+      </c>
+      <c r="F35" s="94" t="s">
+        <v>612</v>
+      </c>
+      <c r="G35" s="94" t="s">
+        <v>614</v>
+      </c>
+      <c r="H35" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="94" t="s">
         <v>616</v>
       </c>
-      <c r="E35" s="109" t="s">
-        <v>619</v>
-      </c>
-      <c r="F35" s="109" t="s">
-        <v>621</v>
-      </c>
-      <c r="G35" s="109" t="s">
-        <v>623</v>
-      </c>
-      <c r="H35" s="109" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="109" t="s">
-        <v>625</v>
-      </c>
-      <c r="J35" s="109" t="s">
-        <v>626</v>
-      </c>
-      <c r="K35" s="109"/>
+      <c r="J35" s="94" t="s">
+        <v>617</v>
+      </c>
+      <c r="K35" s="94"/>
     </row>
     <row r="36" spans="2:11">
       <c r="C36" t="s">
-        <v>632</v>
-      </c>
-      <c r="D36" s="110" t="s">
-        <v>633</v>
-      </c>
-      <c r="E36" s="110" t="s">
-        <v>633</v>
-      </c>
-      <c r="F36" s="110" t="s">
-        <v>633</v>
-      </c>
-      <c r="G36" s="110" t="s">
-        <v>633</v>
-      </c>
-      <c r="H36" s="110" t="s">
-        <v>633</v>
-      </c>
-      <c r="I36" s="110" t="s">
-        <v>633</v>
-      </c>
-      <c r="J36" s="110" t="s">
-        <v>633</v>
+        <v>623</v>
+      </c>
+      <c r="D36" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="E36" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="F36" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="G36" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="H36" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="I36" s="95" t="s">
+        <v>624</v>
+      </c>
+      <c r="J36" s="95" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="C37" t="s">
-        <v>634</v>
-      </c>
-      <c r="H37" s="110" t="s">
-        <v>633</v>
+        <v>625</v>
+      </c>
+      <c r="H37" s="95" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="C38" t="s">
-        <v>635</v>
-      </c>
-      <c r="I38" s="110" t="s">
-        <v>633</v>
+        <v>626</v>
+      </c>
+      <c r="I38" s="95" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="C39" t="s">
-        <v>618</v>
-      </c>
-      <c r="E39" s="110" t="s">
-        <v>633</v>
+        <v>609</v>
+      </c>
+      <c r="E39" s="95" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11409,275 +11770,275 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="D2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="D3" s="89" t="s">
+        <v>584</v>
+      </c>
+      <c r="E3" s="89" t="s">
+        <v>585</v>
+      </c>
+      <c r="F3" s="89" t="s">
+        <v>586</v>
+      </c>
+      <c r="G3" s="89" t="s">
+        <v>588</v>
+      </c>
+      <c r="H3" s="89" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="D4" s="89" t="s">
+        <v>560</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>590</v>
+      </c>
+      <c r="F4" s="89" t="s">
         <v>591</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G4" s="89" t="s">
+        <v>589</v>
+      </c>
+      <c r="H4" s="89" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
-      <c r="D3" s="104" t="s">
+    <row r="5" spans="2:8">
+      <c r="D5" s="91" t="s">
         <v>593</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="E5" s="91" t="s">
         <v>594</v>
       </c>
-      <c r="F3" s="104" t="s">
+      <c r="F5" s="91" t="s">
         <v>595</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G5" s="91" t="s">
+        <v>596</v>
+      </c>
+      <c r="H5" s="91" t="s">
         <v>597</v>
-      </c>
-      <c r="H3" s="104" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="D4" s="104" t="s">
-        <v>569</v>
-      </c>
-      <c r="E4" s="104" t="s">
-        <v>599</v>
-      </c>
-      <c r="F4" s="104" t="s">
-        <v>600</v>
-      </c>
-      <c r="G4" s="104" t="s">
-        <v>598</v>
-      </c>
-      <c r="H4" s="104" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="D5" s="106" t="s">
-        <v>602</v>
-      </c>
-      <c r="E5" s="106" t="s">
-        <v>603</v>
-      </c>
-      <c r="F5" s="106" t="s">
-        <v>604</v>
-      </c>
-      <c r="G5" s="106" t="s">
-        <v>605</v>
-      </c>
-      <c r="H5" s="106" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="D6" s="1" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="D7" s="1" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="D8" s="1" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
     </row>
     <row r="10" spans="2:8">
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="C14" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="C15" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="3:5">
-      <c r="C17" s="105" t="s">
-        <v>582</v>
-      </c>
-      <c r="D17" s="105"/>
+      <c r="C17" s="90" t="s">
+        <v>573</v>
+      </c>
+      <c r="D17" s="90"/>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="105"/>
-      <c r="D18" s="105" t="s">
-        <v>584</v>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="19" spans="3:5">
-      <c r="C19" s="105"/>
-      <c r="D19" s="105" t="s">
-        <v>585</v>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="107" t="s">
-        <v>583</v>
-      </c>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
+      <c r="C21" s="92" t="s">
+        <v>574</v>
+      </c>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
     </row>
     <row r="22" spans="3:5">
-      <c r="C22" s="107"/>
-      <c r="D22" s="107" t="s">
+      <c r="C22" s="92"/>
+      <c r="D22" s="92" t="s">
+        <v>561</v>
+      </c>
+      <c r="E22" s="92"/>
+    </row>
+    <row r="23" spans="3:5">
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5">
+      <c r="C25" s="92"/>
+      <c r="D25" s="92" t="s">
+        <v>562</v>
+      </c>
+      <c r="E25" s="92"/>
+    </row>
+    <row r="26" spans="3:5">
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92" t="s">
         <v>570</v>
       </c>
-      <c r="E22" s="107"/>
-    </row>
-    <row r="23" spans="3:5">
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5">
-      <c r="C24" s="107"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="107" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="25" spans="3:5">
-      <c r="C25" s="107"/>
-      <c r="D25" s="107" t="s">
+    </row>
+    <row r="27" spans="3:5">
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5">
+      <c r="C28" s="92"/>
+      <c r="D28" s="92" t="s">
+        <v>563</v>
+      </c>
+      <c r="E28" s="92" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5">
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5">
+      <c r="C31" s="92"/>
+      <c r="D31" s="92" t="s">
         <v>571</v>
       </c>
-      <c r="E25" s="107"/>
-    </row>
-    <row r="26" spans="3:5">
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5">
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5">
-      <c r="C28" s="107"/>
-      <c r="D28" s="107" t="s">
+      <c r="E31" s="92"/>
+    </row>
+    <row r="32" spans="3:5">
+      <c r="C32" s="92"/>
+      <c r="D32" s="92" t="s">
         <v>572</v>
       </c>
-      <c r="E28" s="107" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5">
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="107" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5">
-      <c r="C30" s="107"/>
-      <c r="D30" s="107"/>
-      <c r="E30" s="107" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5">
-      <c r="C31" s="107"/>
-      <c r="D31" s="107" t="s">
-        <v>580</v>
-      </c>
-      <c r="E31" s="107"/>
-    </row>
-    <row r="32" spans="3:5">
-      <c r="C32" s="107"/>
-      <c r="D32" s="107" t="s">
-        <v>581</v>
-      </c>
-      <c r="E32" s="107"/>
+      <c r="E32" s="92"/>
     </row>
     <row r="33" spans="2:8">
       <c r="C33" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="C34" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="C35" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="H35" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -11705,337 +12066,337 @@
     </row>
     <row r="4" spans="2:23">
       <c r="B4" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="2:23">
       <c r="B5" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="2:23">
       <c r="B6" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="2:23">
       <c r="B7" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="2:23">
       <c r="B8" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="2:23">
       <c r="B9" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="2:23">
       <c r="B10" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="2:23">
       <c r="B11" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="2:23">
       <c r="B12" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U12" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="20"/>
     </row>
     <row r="13" spans="2:23">
       <c r="B13" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="U13" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="20"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U14" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="20"/>
     </row>
     <row r="15" spans="2:23">
       <c r="B15" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="U15" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="20"/>
     </row>
     <row r="16" spans="2:23">
       <c r="B16" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U16" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="20"/>
     </row>
     <row r="17" spans="2:23">
       <c r="B17" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="U17" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="V17" s="20"/>
       <c r="W17" s="20"/>
     </row>
     <row r="18" spans="2:23">
       <c r="B18" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="U18" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="20"/>
     </row>
     <row r="19" spans="2:23">
       <c r="B19" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="U19" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
     </row>
     <row r="20" spans="2:23">
       <c r="B20" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U20" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V20" s="20"/>
       <c r="W20" s="20"/>
     </row>
     <row r="21" spans="2:23">
       <c r="B21" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U21" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="V21" s="20"/>
       <c r="W21" s="20"/>
     </row>
     <row r="22" spans="2:23">
       <c r="B22" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U22" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="20"/>
     </row>
     <row r="23" spans="2:23">
       <c r="B23" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="U23" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="20"/>
     </row>
     <row r="24" spans="2:23">
       <c r="B24" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="U24" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V24" s="20"/>
       <c r="W24" s="20"/>
     </row>
     <row r="25" spans="2:23">
       <c r="B25" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U25" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
     </row>
     <row r="26" spans="2:23">
       <c r="B26" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U26" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
     </row>
     <row r="27" spans="2:23">
       <c r="B27" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="U27" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V27" s="20"/>
       <c r="W27" s="20"/>
     </row>
     <row r="28" spans="2:23">
       <c r="B28" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U28" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
     </row>
     <row r="29" spans="2:23">
       <c r="B29" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U29" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
     </row>
     <row r="30" spans="2:23">
       <c r="B30" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U30" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
     </row>
     <row r="31" spans="2:23">
       <c r="B31" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U31" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V31" s="20"/>
       <c r="W31" s="20"/>
     </row>
     <row r="32" spans="2:23">
       <c r="B32" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="U32" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
     </row>
     <row r="33" spans="2:23">
       <c r="B33" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U33" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
     </row>
     <row r="34" spans="2:23">
       <c r="B34" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="U34" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="V34" s="20"/>
       <c r="W34" s="20"/>
     </row>
     <row r="35" spans="2:23">
       <c r="B35" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="2:23">
       <c r="B36" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="2:23">
       <c r="B37" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="2:23">
       <c r="B38" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="2:23">
       <c r="B39" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="2:23">
       <c r="B40" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="2:23">
       <c r="B41" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="2:23">
       <c r="B42" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="2:23">
       <c r="B43" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="2:23">
       <c r="B44" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="2:23">
       <c r="B45" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="2:23">
       <c r="B46" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="2:23">
       <c r="B47" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -13172,7 +13533,7 @@
     </row>
     <row r="243" spans="2:2" ht="16">
       <c r="B243" s="13" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244" spans="2:2">
